--- a/data/credit_bond_all_2026-09-24.xlsx
+++ b/data/credit_bond_all_2026-09-24.xlsx
@@ -159,7 +159,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AZ41"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr defaultRowHeight="18.0" baseColWidth="12" customHeight="true"/>
   <cols>
     <col min="1" max="1" width="12.0" customWidth="true"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1383,14 +1383,22 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>25中核二二GN001(科创债)</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>2.24Y+2.00Y</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1431,7 +1439,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X6" s="3"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.95%~2.05%</t>
+        </is>
+      </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -1647,7 +1659,11 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X7" s="3"/>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>1.93%~2.03%</t>
+        </is>
+      </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -1784,7 +1800,11 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>012682359.IB</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -1863,7 +1883,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X8" s="3"/>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2000,7 +2024,11 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>012682355.IB</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -2079,7 +2107,11 @@
           <t>6+</t>
         </is>
       </c>
-      <c r="X9" s="3"/>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -2216,7 +2248,11 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C10" s="3"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>102683834.IB</t>
+        </is>
+      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
           <t>10Y</t>
@@ -2255,7 +2291,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9225/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -2295,7 +2331,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>1.94%~2.04%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2438,7 +2478,11 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>012682352.IB</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
@@ -2517,7 +2561,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="X11" s="3"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2654,7 +2702,11 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>012682354.IB</t>
+        </is>
+      </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
           <t>0.08Y</t>
@@ -2693,7 +2745,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4600</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
@@ -2733,7 +2785,11 @@
           <t>4+</t>
         </is>
       </c>
-      <c r="X12" s="3"/>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.45%~1.49%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -2870,7 +2926,11 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>102683839.IB</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -2909,7 +2969,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -2949,7 +3009,11 @@
           <t>5+</t>
         </is>
       </c>
-      <c r="X13" s="3"/>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3090,7 +3154,11 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>102683833.IB</t>
+        </is>
+      </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
@@ -3129,7 +3197,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7600</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3169,7 +3237,11 @@
           <t>5-</t>
         </is>
       </c>
-      <c r="X14" s="3"/>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.70%~1.80%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -3302,7 +3374,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN008B(绿色科创债)</t>
+          <t>26南电GN008(科创债)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3310,56 +3382,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>132680099.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN007B(科创债)</t>
+          <t>26南电GN007(科创债)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7410</t>
+          <t>1.6296</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司</t>
+          <t>中国南方电网有限责任公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 40.04</t>
+          <t>B- 38.72</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3386,10 +3462,14 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X15" s="3"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>1.64%~1.74%</t>
+        </is>
+      </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3398,17 +3478,17 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>福建省-宁德市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
+          <t>本期绿色科技创新债券发行规模20亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营以及充电站项目建设</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3419,7 +3499,7 @@
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
@@ -3429,7 +3509,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种二)</t>
+          <t>中国南方电网有限责任公司2026年度第八期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3439,14 +3519,10 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK15" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-22</t>
+        </is>
+      </c>
+      <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3469,27 +3545,27 @@
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>电源设备</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3522,7 +3598,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN002(并购)</t>
+          <t>26环球天津SCP005</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3530,41 +3606,45 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C16" s="3"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>012682360.IB</t>
+        </is>
+      </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.47Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.32 ~ 1.62</t>
         </is>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN001(科创债)</t>
+          <t>26环球天津SCP003</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7555</t>
+          <t>1.6380</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3574,12 +3654,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司</t>
+          <t>通用环球国际融资租赁(天津)有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>A 80.00</t>
+          <t>C- 10.79</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3606,10 +3686,14 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X16" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>1.63%~1.67%</t>
+        </is>
+      </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3618,28 +3702,28 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
+          <t>本期超短期融资券发行金额为5亿元,用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
+          <t>渤海银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3649,7 +3733,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司2026年度第二期科技创新债券(并购)</t>
+          <t>通用环球国际融资租赁(天津)有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3659,14 +3743,10 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-03-19</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3684,32 +3764,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3727,18 +3807,24 @@
           <t>不含权</t>
         </is>
       </c>
-      <c r="AX16" s="3"/>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
       <c r="AY16" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26南电MTN008(绿色科创债)</t>
+          <t>26京国资SCP001</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3746,56 +3832,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>012682356.IB</t>
+        </is>
+      </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26南电GN007(科创债)</t>
+          <t>24国管01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>330D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.6296</t>
+          <t>1.4842</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5100</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司</t>
+          <t>北京国有资本运营管理有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 38.72</t>
+          <t>B- 37.61</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3805,7 +3895,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3822,40 +3912,48 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X17" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z17" s="3"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模20亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营以及充电站项目建设</t>
+          <t>本期债务融资工具发行规模为人民币10亿元，发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -3865,7 +3963,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司2026年度第八期绿色科技创新债券</t>
+          <t>北京国有资本运营管理有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -3875,7 +3973,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
@@ -3901,27 +3999,27 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -3954,7 +4052,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26环球天津SCP005</t>
+          <t>26夏商SCP028</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -3962,10 +4060,14 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C18" s="3"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>012682357.IB</t>
+        </is>
+      </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>0.47Y</t>
+          <t>0.22Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -3974,44 +4076,44 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.62</t>
+          <t>1.21 ~ 1.51</t>
         </is>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26环球天津SCP003</t>
+          <t>26夏商SCP026</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>78D</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.6380</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.4900</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>通用环球国际融资租赁(天津)有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C- 10.79</t>
+          <t>B- 49.30</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4038,29 +4140,33 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X18" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为5亿元,用于偿还发行人存量有息债务</t>
+          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于用于补充发行人子公司厦门夏商民昇贸易有限公司营运资金。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4071,7 +4177,7 @@
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4081,7 +4187,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>通用环球国际融资租赁(天津)有限公司2026年度第五期超短期融资券</t>
+          <t>厦门夏商集团有限公司2026年度第二十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4091,10 +4197,14 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2027-03-19</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -4112,32 +4222,32 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4165,12 +4275,14 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ18" s="3"/>
+      <c r="AZ18" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26京国资SCP001</t>
+          <t>26衢产PPN001</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4181,53 +4293,53 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>24国管01</t>
+          <t>26衢产02</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>330D</t>
+          <t>2.67Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.4842</t>
+          <t>1.7164</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司</t>
+          <t>衢州市产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 37.61</t>
+          <t>B- 38.13</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4237,7 +4349,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 10:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4247,46 +4359,46 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X19" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
+      <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-衢州市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币10亿元，发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
+          <t>本期发行人发行的定向债务融资工具基础发行规模为0亿元,发行金额上限为5亿元,募集资金拟全部用于偿还公司银行贷款。[23衢州控股PPN001]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,杭州银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,恒丰银行股份有限公司,财通证券股份有限公司,上海银行股份有限公司,中信银行股份有限公司,宁波银行股份有限公司,中国建设银行股份有限公司,上海浦东发展银行股份有限公司,浙商银行股份有限公司,南京银行股份有限公司,徽商银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4301,35 +4413,39 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司2026年度第一期超短期融资券</t>
+          <t>衢州市产业投资控股集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -4337,7 +4453,7 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
@@ -4390,7 +4506,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP028</t>
+          <t>26润业投资PPN002B</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4401,53 +4517,53 @@
       <c r="C20" s="3"/>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>0.22Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.21 ~ 1.51</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP026</t>
+          <t>26润业01</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>78D</t>
+          <t>2.52Y+2.00Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.8400</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8900/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>河源市润业投资有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 49.30</t>
+          <t>C- 15.95</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4457,7 +4573,7 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
@@ -4474,10 +4590,14 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X20" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>1.90%~2.00%</t>
+        </is>
+      </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4486,23 +4606,23 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>广东省-河源市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于用于补充发行人子公司厦门夏商民昇贸易有限公司营运资金。</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4517,22 +4637,22 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十八期超短期融资券</t>
+          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种二)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK20" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL20" s="3" t="inlineStr">
@@ -4552,32 +4672,32 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8.5*无效</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4605,14 +4725,12 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ20" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ20" s="3"/>
     </row>
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26衢产PPN001</t>
+          <t>26海螺集团MTN002(科创债/并购)</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4620,19 +4738,23 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C21" s="3"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>102683838.IB</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H21" s="3"/>
@@ -4644,17 +4766,17 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26衢产02</t>
+          <t>26海螺集团MTN001(科创债)</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.67Y</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7164</t>
+          <t>1.7555</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4664,12 +4786,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>衢州市产业投资控股集团有限公司</t>
+          <t>安徽海螺集团有限责任公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 38.13</t>
+          <t>A 80.00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4679,7 +4801,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-24 10:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4689,17 +4811,21 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X21" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4708,23 +4834,23 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>浙江省-衢州市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期发行人发行的定向债务融资工具基础发行规模为0亿元,发行金额上限为5亿元,募集资金拟全部用于偿还公司银行贷款。[23衢州控股PPN001]</t>
+          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,杭州银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,恒丰银行股份有限公司,财通证券股份有限公司,上海银行股份有限公司,中信银行股份有限公司,宁波银行股份有限公司,中国建设银行股份有限公司,上海浦东发展银行股份有限公司,浙商银行股份有限公司,南京银行股份有限公司,徽商银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -4739,27 +4865,27 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>衢州市产业投资控股集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>安徽海螺集团有限责任公司2026年度第二期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK21" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
@@ -4769,7 +4895,7 @@
       </c>
       <c r="AN21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO21" s="3" t="inlineStr">
@@ -4779,27 +4905,27 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -4832,7 +4958,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26润业投资PPN002B</t>
+          <t>26宁德时代MTN008B(科创债)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -4840,41 +4966,45 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C22" s="3"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>102683832.IB</t>
+        </is>
+      </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.5</v>
+        <v>25.0</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26润业01</t>
+          <t>26宁德时代MTN007B(科创债)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.52Y+2.00Y</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.8400</t>
+          <t>1.7410</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -4884,12 +5014,12 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司</t>
+          <t>宁德时代新能源科技股份有限公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>C- 15.95</t>
+          <t>B- 40.04</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -4899,7 +5029,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -4916,40 +5046,44 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X22" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>1.69%~1.79%</t>
+        </is>
+      </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>广东省-河源市</t>
+          <t>福建省-宁德市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
+          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -4959,12 +5093,12 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种二)</t>
+          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种二)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
@@ -4994,32 +5128,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>8.5*无效</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电源设备</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5052,66 +5186,68 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26浙商证券CP006</t>
+          <t>26句容03</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>072610196.IB</t>
+          <t>283950.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0.66Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4" t="n">
-        <v>1.52</v>
-      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26浙商证券CP005</t>
+          <t>26句容01</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>274D</t>
+          <t>4.72Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.5251</t>
+          <t>2.0026</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1000/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>江苏句容福地生态科技有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B- 36.94</t>
+          <t>B- 35.73</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5121,7 +5257,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5138,35 +5274,39 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
-        </is>
-      </c>
-      <c r="AB23" s="3"/>
+          <t>江苏省-镇江市</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟将9.00亿元用于偿还回售的公司债券本金[23句容04]</t>
+        </is>
+      </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
@@ -5176,28 +5316,32 @@
       </c>
       <c r="AG23" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司2026年度第六期短期融资券</t>
+          <t>江苏句容福地生态科技有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2027-05-26</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5212,32 +5356,32 @@
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5270,51 +5414,45 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP010</t>
+          <t>26港兴01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>072610197.IB</t>
+          <t>283963.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>0.91Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4" t="n">
-        <v>1.51</v>
-      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>26国泰海通CP006</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>264D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K24" s="3"/>
+      <c r="L24" s="3"/>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.4951</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5324,14 +5462,10 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="inlineStr">
-        <is>
-          <t>A- 68.49</t>
-        </is>
-      </c>
+          <t>响水县港兴建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="P24" s="3"/>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -5339,7 +5473,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5354,37 +5488,33 @@
       </c>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
-      <c r="W24" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t>1.48%~1.52%</t>
-        </is>
-      </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB24" s="3"/>
+          <t>江苏省-盐城市</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用和受托管理费用后,拟全部用于偿还到期债务。</t>
+        </is>
+      </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD24" s="3"/>
+          <t>开源证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>江苏省信用增进有限责任公司</t>
+        </is>
+      </c>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
@@ -5394,33 +5524,37 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第十期短期融资券</t>
+          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
-        </is>
-      </c>
-      <c r="AK24" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK24" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
@@ -5430,32 +5564,28 @@
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP24" s="3"/>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5465,7 +5595,7 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW24" s="3" t="inlineStr">
@@ -5488,7 +5618,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26锡铁01</t>
+          <t>26港兴02</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5498,7 +5628,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>284118.SH</t>
+          <t>283964.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5507,34 +5637,26 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>26锡铁D1</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>315D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.5279</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5544,14 +5666,10 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>无锡地铁集团有限公司</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t>C- 25.00</t>
-        </is>
-      </c>
+          <t>响水县港兴建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="P25" s="3"/>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -5574,38 +5692,30 @@
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t>1.74%~1.84%</t>
-        </is>
-      </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于置换自有资金偿还的公司债券本金[GY锡铁01]</t>
+          <t>本期债券募集资金扣除发行费用和受托管理费用后,拟全部用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,中信建投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3"/>
+          <t>开源证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr">
+        <is>
+          <t>湖南财鑫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5623,7 +5733,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>无锡地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5648,7 +5758,7 @@
       </c>
       <c r="AM25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN25" s="3" t="inlineStr">
@@ -5658,32 +5768,28 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP25" s="3"/>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5693,7 +5799,7 @@
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
@@ -5716,7 +5822,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26同舟02</t>
+          <t>26方大01</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5726,48 +5832,60 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>283937.SH</t>
+          <t>284123.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.5</v>
+        <v>10.0</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
+          <t>4.30 ~ 6.30</t>
         </is>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>24辽宁方大MTN001</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>218D</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>5.9380</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>6.0000/5.5000</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P26" s="3"/>
+          <t>辽宁方大集团实业有限公司</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>B 55.00</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -5798,23 +5916,23 @@
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
+          <t>本期债券发行规模为不超过人民币10.00亿元(含10.00亿元),债券募集资金扣除发行费用后,拟全部用于偿还到期的有息债务。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
+          <t>中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -5825,7 +5943,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -5835,7 +5953,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>辽宁方大集团实业有限公司2026年面向专业投资者非公开发行公司债券(高成长产业债)(第一期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -5845,10 +5963,14 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
-        </is>
-      </c>
-      <c r="AK26" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5856,7 +5978,7 @@
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
@@ -5869,30 +5991,34 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP26" s="3"/>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="AV26" s="3" t="inlineStr">
@@ -5920,7 +6046,7 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26中交三航SCP023</t>
+          <t>26郑州交发MTN002(绿色)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -5928,10 +6054,14 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>102683830.IB</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
@@ -5940,44 +6070,44 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>26中交三航SCP019</t>
+          <t>24郑州地铁GN002</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>97D</t>
+          <t>1.12Y+N</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.5002</t>
+          <t>1.6185</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>中交第三航务工程局有限公司</t>
+          <t>郑州交通发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.09</t>
+          <t>C- 20.57</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6004,10 +6134,14 @@
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X27" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6016,28 +6150,28 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为5亿元，全部用于归还发行人本部有息负债</t>
+          <t>本期发行金额上限10.00亿元,基础发行规模0亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
@@ -6047,7 +6181,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>中交第三航务工程局有限公司2026年度第二十三期超短期融资券</t>
+          <t>郑州交通发展投资集团有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6057,7 +6191,7 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6078,32 +6212,32 @@
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6118,12 +6252,12 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY27" s="3" t="inlineStr">
@@ -6131,56 +6265,56 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ27" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ27" s="3"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN001</t>
+          <t>26浙商证券CP006</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
-        </is>
-      </c>
-      <c r="C28" s="3"/>
+          <t>09-24 17:00</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>072610196.IB</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.66Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="F28" s="3"/>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>1.20 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="4" t="n">
+        <v>1.52</v>
+      </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>26浙商证券CP005</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.21Y</t>
+          <t>274D</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.6011</t>
+          <t>1.5251</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6190,12 +6324,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 49.82</t>
+          <t>B- 36.94</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6222,10 +6356,14 @@
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X28" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6234,28 +6372,24 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB28" s="3" t="inlineStr">
-        <is>
-          <t>本期中期票据发行金额为16亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金。</t>
-        </is>
-      </c>
+          <t>浙江省-杭州市</t>
+        </is>
+      </c>
+      <c r="AB28" s="3"/>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6265,7 +6399,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第一期中期票据</t>
+          <t>浙商证券股份有限公司2026年度第六期短期融资券</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6275,7 +6409,7 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2027-05-26</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
@@ -6296,32 +6430,32 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6354,64 +6488,66 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN003(并购)</t>
+          <t>26国泰海通CP010</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
-        </is>
-      </c>
-      <c r="C29" s="3"/>
+          <t>09-24 17:00</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>072610197.IB</t>
+        </is>
+      </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.91Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="4" t="n">
+        <v>1.51</v>
+      </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN001(科创债)</t>
+          <t>26国泰海通CP006</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>264D</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.7555</t>
+          <t>1.4951</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>A 80.00</t>
+          <t>A- 68.49</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6438,10 +6574,14 @@
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X29" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>1.48%~1.52%</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6450,23 +6590,19 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
-        </is>
-      </c>
-      <c r="AB29" s="3" t="inlineStr">
-        <is>
-          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
-        </is>
-      </c>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB29" s="3"/>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6481,7 +6617,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司2026年度第三期科技创新债券(并购)</t>
+          <t>国泰海通证券股份有限公司2026年度第十期短期融资券</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6491,14 +6627,10 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK29" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-08-26</t>
+        </is>
+      </c>
+      <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -6516,32 +6648,32 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6574,7 +6706,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26乌江水电SCP005(绿色)</t>
+          <t>26锡铁01</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6582,41 +6714,45 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C30" s="3"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>284118.SH</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.65</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26乌江水电GN002</t>
+          <t>26锡铁D1</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>179D</t>
+          <t>315D</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5294</t>
+          <t>1.5279</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6626,12 +6762,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江水电开发有限责任公司</t>
+          <t>无锡地铁集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C 26.67</t>
+          <t>C- 25.00</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6641,7 +6777,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6658,10 +6794,14 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X30" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6670,59 +6810,63 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期绿色超短期融资券发行金额3亿元,募集资金将全部用于偿还构皮滩水电站等6个水电站有息负债本金</t>
+          <t>本期债券募集资金拟全部用于置换自有资金偿还的公司债券本金[GY锡铁01]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,招商银行股份有限公司</t>
+          <t>天风证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江水电开发有限责任公司2026年度第五期绿色超短期融资券</t>
+          <t>无锡地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK30" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK30" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -6732,32 +6876,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6790,7 +6934,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26郑州交发MTN002(绿色)</t>
+          <t>26同舟02</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -6798,58 +6942,58 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C31" s="3"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>283937.SH</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>10.0</v>
+        <v>3.5</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.80 ~ 2.40</t>
         </is>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24郑州地铁GN002</t>
+          <t>25中核二二GN001(科创债)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>1.12Y+N</t>
+          <t>2.24Y+2.00Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.6185</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t>C- 20.57</t>
-        </is>
-      </c>
+          <t>山东同舟产业控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P31" s="3"/>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -6857,7 +7001,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
@@ -6867,17 +7011,21 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X31" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>2.30%~2.40%</t>
+        </is>
+      </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -6886,23 +7034,23 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额上限10.00亿元,基础发行规模0亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
+          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
+          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -6912,73 +7060,69 @@
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司2026年度第二期绿色中期票据</t>
+          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2036-09-29</t>
         </is>
       </c>
       <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP31" s="3"/>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -6988,12 +7132,12 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY31" s="3" t="inlineStr">
@@ -7006,7 +7150,7 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26柯资03</t>
+          <t>26中交三航SCP023</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -7016,43 +7160,43 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>284115.SH</t>
+          <t>012682353.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26柯资02</t>
+          <t>26中交三航SCP019</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>97D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6924</t>
+          <t>1.5002</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7062,12 +7206,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区国有资产投资经营集团有限公司</t>
+          <t>中交第三航务工程局有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.01</t>
+          <t>C+ 30.09</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7077,7 +7221,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -7094,113 +7238,117 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X32" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过10亿元(含10亿元),募集资金拟全部用于偿还到期公司债券的本金。[23柯资05,23柯资06]</t>
+          <t>本期发行金额为5亿元，全部用于归还发行人本部有息负债</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>广发银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>中交第三航务工程局有限公司2026年度第二十三期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2026-12-29</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>市政路桥</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7221,73 +7369,75 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ32" s="3"/>
+      <c r="AZ32" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26柯桥03</t>
+          <t>26东航股MTN001</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>284145.SH</t>
+          <t>102683837.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>20.0</v>
+        <v>16.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.20 ~ 1.80</t>
         </is>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26绍兴柯桥PPN001</t>
+          <t>25东航股MTN006</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>4.44Y</t>
+          <t>2.21Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.9325</t>
+          <t>1.6011</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区建设集团有限公司</t>
+          <t>中国东方航空股份有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C 28.59</t>
+          <t>B- 49.82</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7297,7 +7447,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7314,113 +7464,117 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X33" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>1.59%~1.69%</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23柯桥01]</t>
+          <t>本期中期票据发行金额为16亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金。</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国投证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区建设集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>中国东方航空股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2033-09-28</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
       <c r="AL33" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>航空</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>航空运输</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO33" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ33" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR33" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
       <c r="AV33" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7428,7 +7582,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7446,7 +7600,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP027</t>
+          <t>26海螺集团MTN003(科创债/并购)</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7454,41 +7608,45 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C34" s="3"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>102683836.IB</t>
+        </is>
+      </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.51</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP026</t>
+          <t>26海螺集团MTN001(科创债)</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>78D</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.7555</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7498,12 +7656,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>安徽海螺集团有限责任公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 49.30</t>
+          <t>A 80.00</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7530,35 +7688,39 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X34" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>1.72%~1.82%</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元,扣除承销费后全部用于偿还发行人即将到期的债务融资工具。[26夏商SCP020]</t>
+          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7573,7 +7735,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十七期超短期融资券</t>
+          <t>安徽海螺集团有限责任公司2026年度第三期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7583,10 +7745,14 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
-        </is>
-      </c>
-      <c r="AK34" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -7609,27 +7775,27 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -7662,7 +7828,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26京国资SCP002</t>
+          <t>26乌江水电GN005</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7670,56 +7836,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C35" s="3"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>132680100.IB</t>
+        </is>
+      </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
           <t>0.74Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.40 ~ 1.65</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>24国管01</t>
+          <t>26乌江水电GN002</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>330D</t>
+          <t>179D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.4842</t>
+          <t>1.5294</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司</t>
+          <t>贵州乌江水电开发有限责任公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B- 37.61</t>
+          <t>C 26.67</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -7729,7 +7899,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -7746,33 +7916,33 @@
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X35" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>1.49%~1.53%</t>
+        </is>
+      </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
+      <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币10亿元,发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
+          <t>本期绿色超短期融资券发行金额3亿元,募集资金将全部用于偿还构皮滩水电站等6个水电站有息负债本金</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司,北京农村商业银行股份有限公司</t>
+          <t>中国银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
@@ -7783,7 +7953,7 @@
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -7793,7 +7963,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司2026年度第二期超短期融资券</t>
+          <t>贵州乌江水电开发有限责任公司2026年度第五期绿色超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7829,27 +7999,27 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -7882,7 +8052,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26湖交投MTN004</t>
+          <t>26柯资03</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -7890,56 +8060,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C36" s="3"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>284115.SH</t>
+        </is>
+      </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26湖交投MTN003</t>
+          <t>26柯资02</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+2.00Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.6831</t>
+          <t>1.6924</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7300/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>湖州市交通投资集团有限公司</t>
+          <t>绍兴市柯桥区国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B- 38.74</t>
+          <t>C+ 31.01</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -7949,7 +8123,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -7966,35 +8140,39 @@
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模为0亿元,发行金额上限为5.00亿元,拟全部用于偿还发行人债务融资工具本金[23湖交投MTN004]</t>
+          <t>本期债券发行规模为不超过10亿元(含10亿元),募集资金拟全部用于偿还到期公司债券的本金。[23柯资05,23柯资06]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,招商银行股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8004,32 +8182,28 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>湖州市交通投资集团有限公司2026年度第四期中期票据</t>
+          <t>绍兴市柯桥区国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK36" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8044,37 +8218,37 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8084,7 +8258,7 @@
       </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX36" s="3" t="inlineStr">
@@ -8102,68 +8276,68 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26惠鑫01</t>
+          <t>26柯桥03</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:30</t>
+          <t>09-24 17:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>284108.SH</t>
+          <t>284145.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>7.57</v>
+        <v>20.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>25惠鑫01</t>
+          <t>26绍兴柯桥PPN001</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>3.66Y</t>
+          <t>4.44Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.8399</t>
+          <t>1.9325</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9700/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>无锡惠鑫汇资产经营管理有限公司</t>
+          <t>绍兴市柯桥区建设集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>D- 0.72</t>
+          <t>C 28.59</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8183,36 +8357,40 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X37" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟将募集资金7.57亿元用于偿还到期公司债券本金[24惠鑫01,23惠鑫04]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23柯桥01]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天风证券股份有限公司</t>
+          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8233,7 +8411,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>无锡惠鑫汇资产经营管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>绍兴市柯桥区建设集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8243,7 +8421,7 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2033-09-28</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
@@ -8259,7 +8437,7 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
@@ -8269,7 +8447,7 @@
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
@@ -8289,12 +8467,12 @@
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8304,7 +8482,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8322,7 +8500,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26靖江滨江PPN002</t>
+          <t>26夏商SCP027</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8330,56 +8508,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C38" s="3"/>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>012682361.IB</t>
+        </is>
+      </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.38 ~ 2.10</t>
+          <t>1.40 ~ 1.51</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>25靖滨03</t>
+          <t>26夏商SCP026</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>78D</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6599</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.4900</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 23.01</t>
+          <t>B- 49.30</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8406,35 +8588,39 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X38" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额2.5亿元,用于置换有息债务[26靖江滨江SCP001]</t>
+          <t>发行人本期发行超短期融资券5亿元,扣除承销费后全部用于偿还发行人即将到期的债务融资工具。[26夏商SCP020]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8449,17 +8635,17 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年度第二期定向债务融资工具</t>
+          <t>厦门夏商集团有限公司2026年度第二十七期超短期融资券</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2028-09-28</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
@@ -8480,32 +8666,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8538,7 +8724,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26润业投资PPN002A</t>
+          <t>26京国资SCP002</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8546,56 +8732,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C39" s="3"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>012682358.IB</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2.5</v>
+        <v>10.0</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26润业01</t>
+          <t>24国管01</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.52Y+2.00Y</t>
+          <t>330D</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.8400</t>
+          <t>1.4842</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5300/1.5100</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司</t>
+          <t>北京国有资本运营管理有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>C- 15.95</t>
+          <t>B- 37.61</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8605,7 +8795,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8622,35 +8812,43 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X39" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z39" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>广东省-河源市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
+          <t>本期债务融资工具发行规模为人民币10亿元,发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>华夏银行股份有限公司,北京农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -8665,24 +8863,20 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种一)</t>
+          <t>北京国有资本运营管理有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK39" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-25</t>
+        </is>
+      </c>
+      <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -8700,37 +8894,37 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>8.5*无效</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV39" s="3" t="inlineStr">
@@ -8740,7 +8934,7 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -8758,7 +8952,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26东阳国资PPN002</t>
+          <t>26湖交投MTN004</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -8766,10 +8960,14 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C40" s="3"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>102683835.IB</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -8778,44 +8976,44 @@
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26东阳国资PPN001A</t>
+          <t>26湖交投MTN003</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>2.98Y+2.00Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.8376</t>
+          <t>1.6831</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6900/1.6400</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>东阳市国有资产投资有限公司</t>
+          <t>湖州市交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 17.96</t>
+          <t>B- 38.74</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -8825,7 +9023,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -8842,35 +9040,39 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X40" s="3"/>
+          <t>5+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>1.60%~1.70%</t>
+        </is>
+      </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行规模为人民币5亿元，用于偿还有息负债[23东阳国资PPN003]</t>
+          <t>发行人本期中期票据基础发行规模为0亿元,发行金额上限为5.00亿元,拟全部用于偿还发行人债务融资工具本金[23湖交投MTN004]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司</t>
+          <t>东方证券股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -8885,12 +9087,12 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>东阳市国有资产投资有限公司2026年度第二期定向债务融资工具</t>
+          <t>湖州市交通投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
@@ -8920,37 +9122,37 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV40" s="3" t="inlineStr">
@@ -8960,7 +9162,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -8978,49 +9180,53 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN008A(绿色科创债)</t>
+          <t>26惠鑫01</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
-        </is>
-      </c>
-      <c r="C41" s="3"/>
+          <t>09-24 17:30</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>284108.SH</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>25.0</v>
+        <v>7.57</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN007A(科创债)</t>
+          <t>25惠鑫01</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.99Y+2.00Y</t>
+          <t>3.66Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.6700</t>
+          <t>1.8399</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -9030,12 +9236,12 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司</t>
+          <t>无锡惠鑫汇资产经营管理有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 40.04</t>
+          <t>D- 0.72</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9045,7 +9251,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9055,145 +9261,1489 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X41" s="3"/>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>福建省-宁德市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
+          <t>本期债券拟将募集资金7.57亿元用于偿还到期公司债券本金[24惠鑫01,23惠鑫04]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>东吴证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr">
+        <is>
+          <t>无锡惠鑫汇资产经营管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK41" s="3"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AZ41" s="3"/>
+    </row>
+    <row r="42" customHeight="true" ht="18.0">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>26靖江滨江PPN002</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>09-24 18:00</t>
+        </is>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>1.38 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>25靖滨03</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>1.88Y</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>1.6599</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>--/1.6100</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>靖江市滨江新城投资开发有限公司</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>C- 23.01</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>09-24 09:00</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>1.68%~1.78%</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-泰州市</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>本期定向债务融资工具发行金额2.5亿元,用于置换有息债务[26靖江滨江SCP001]</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>江苏银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD42" s="3"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>靖江市滨江新城投资开发有限公司2026年度第二期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr">
+        <is>
+          <t>2028-09-28</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY42" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AZ42" s="3"/>
+    </row>
+    <row r="43" customHeight="true" ht="18.0">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>26润业投资PPN002A</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>09-24 18:00</t>
+        </is>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>26润业01</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>2.52Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>1.8400</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>1.8900/--</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>河源市润业投资有限公司</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>C- 15.95</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>09-24 15:00</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U43" s="3"/>
+      <c r="V43" s="3"/>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.92%</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>广东省-河源市</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>中信建投证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr">
+        <is>
+          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种一)</t>
+        </is>
+      </c>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK43" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>8.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY43" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AZ43" s="3"/>
+    </row>
+    <row r="44" customHeight="true" ht="18.0">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>26东阳国资PPN002</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>09-24 18:00</t>
+        </is>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>26东阳国资PPN001A</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>4.50Y</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1.8376</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>--/1.8000</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>东阳市国有资产投资有限公司</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>C- 17.96</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>09-24 09:00</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U44" s="3"/>
+      <c r="V44" s="3"/>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1.82%~1.92%</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>浙江省-金华市</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>发行人本期拟发行规模为人民币5亿元，用于偿还有息负债[23东阳国资PPN003]</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>中信银行股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD44" s="3"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>定向工具(PPN)</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>银行间</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr">
+        <is>
+          <t>东阳市国有资产投资有限公司2026年度第二期定向债务融资工具</t>
+        </is>
+      </c>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AZ44" s="3"/>
+    </row>
+    <row r="45" customHeight="true" ht="18.0">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>26宁德时代MTN008A(科创债)</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>09-24 18:00</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>102683831.IB</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>1.40 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>26宁德时代MTN007A(科创债)</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>2.99Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>1.6700</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>1.6900/1.6700</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>宁德时代新能源科技股份有限公司</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>B- 40.04</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>09-24 09:00</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U45" s="3"/>
+      <c r="V45" s="3"/>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>1.61%~1.71%</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>福建省-宁德市</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD45" s="3"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
           <t>中期票据</t>
         </is>
       </c>
-      <c r="AF41" s="3" t="inlineStr">
+      <c r="AF45" s="3" t="inlineStr">
         <is>
           <t>民营企业</t>
         </is>
       </c>
-      <c r="AG41" s="3" t="inlineStr">
+      <c r="AG45" s="3" t="inlineStr">
         <is>
           <t>银行间</t>
         </is>
       </c>
-      <c r="AH41" s="3" t="inlineStr">
+      <c r="AH45" s="3" t="inlineStr">
         <is>
           <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种一)</t>
         </is>
       </c>
-      <c r="AI41" s="3" t="inlineStr">
+      <c r="AI45" s="3" t="inlineStr">
         <is>
           <t>公募</t>
         </is>
       </c>
-      <c r="AJ41" s="3" t="inlineStr">
+      <c r="AJ45" s="3" t="inlineStr">
         <is>
           <t>2031-09-28</t>
         </is>
       </c>
-      <c r="AK41" s="3" t="inlineStr">
+      <c r="AK45" s="3" t="inlineStr">
         <is>
           <t>休1</t>
         </is>
       </c>
-      <c r="AL41" s="3" t="inlineStr">
+      <c r="AL45" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
+      <c r="AM45" s="3" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
+      <c r="AN45" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="AO41" s="3" t="inlineStr">
+      <c r="AO45" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
+      <c r="AP45" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AQ41" s="3" t="inlineStr">
+      <c r="AQ45" s="3" t="inlineStr">
         <is>
           <t>电力设备制造</t>
         </is>
       </c>
-      <c r="AR41" s="3" t="inlineStr">
+      <c r="AR45" s="3" t="inlineStr">
         <is>
           <t>其他电力设备</t>
         </is>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
+      <c r="AS45" s="3" t="inlineStr">
         <is>
           <t>其他电力设备</t>
         </is>
       </c>
-      <c r="AT41" s="3" t="inlineStr">
+      <c r="AT45" s="3" t="inlineStr">
         <is>
           <t>电源设备</t>
         </is>
       </c>
-      <c r="AU41" s="3" t="inlineStr">
+      <c r="AU45" s="3" t="inlineStr">
         <is>
           <t>2029-09-28</t>
         </is>
       </c>
-      <c r="AV41" s="3" t="inlineStr">
+      <c r="AV45" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
         </is>
       </c>
-      <c r="AW41" s="3" t="inlineStr">
+      <c r="AW45" s="3" t="inlineStr">
         <is>
           <t>含权</t>
         </is>
       </c>
-      <c r="AX41" s="3" t="inlineStr">
+      <c r="AX45" s="3" t="inlineStr">
         <is>
           <t>普通债权</t>
         </is>
       </c>
-      <c r="AY41" s="3" t="inlineStr">
+      <c r="AY45" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ41" s="3"/>
+      <c r="AZ45" s="3"/>
+    </row>
+    <row r="46" customHeight="true" ht="18.0">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>26澄港01</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>09-24 18:00</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>525027.SZ</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>24江阴临港MTN001</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>1.14Y</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>1.5659</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>江阴临港新城开发建设有限公司</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>C+ 32.94</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>09-24 16:00</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U46" s="3"/>
+      <c r="V46" s="3"/>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X46" s="3"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3" t="inlineStr">
+        <is>
+          <t>江苏省-无锡市</t>
+        </is>
+      </c>
+      <c r="AB46" s="3" t="inlineStr">
+        <is>
+          <t>本期债券发行总额不超过8.00亿元,公司仅可将本期债券募集资金用于偿还到期公司债券本金[21澄港04]</t>
+        </is>
+      </c>
+      <c r="AC46" s="3" t="inlineStr">
+        <is>
+          <t>中信证券股份有限公司,东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
+      <c r="AE46" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF46" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG46" s="3" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="AH46" s="3" t="inlineStr">
+        <is>
+          <t>江阴临港新城开发建设有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI46" s="3" t="inlineStr">
+        <is>
+          <t>公募</t>
+        </is>
+      </c>
+      <c r="AJ46" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK46" s="3"/>
+      <c r="AL46" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>有担保</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AZ46" s="3"/>
+    </row>
+    <row r="47" customHeight="true" ht="18.0">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>26郑经K1</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>09-24 18:00</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>284034.SH</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>3+2</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>26郑经01</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>2.31Y+2.00Y</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>1.7867</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>1.8200/1.6600</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>郑州经开资本集团有限公司</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>D+ 10.00</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>09-24 16:00</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="T47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U47" s="3"/>
+      <c r="V47" s="3"/>
+      <c r="W47" s="3" t="inlineStr">
+        <is>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X47" s="3"/>
+      <c r="Y47" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3" t="inlineStr">
+        <is>
+          <t>河南省-郑州市</t>
+        </is>
+      </c>
+      <c r="AB47" s="3" t="inlineStr">
+        <is>
+          <t>本期债券募集资金扣除发行费用后,拟将不低于0.70亿元募集资金通过发行人本部或子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余资金用于偿还有息负债。</t>
+        </is>
+      </c>
+      <c r="AC47" s="3" t="inlineStr">
+        <is>
+          <t>申万宏源证券有限公司,东兴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD47" s="3"/>
+      <c r="AE47" s="3" t="inlineStr">
+        <is>
+          <t>公司债券</t>
+        </is>
+      </c>
+      <c r="AF47" s="3" t="inlineStr">
+        <is>
+          <t>地方国有企业</t>
+        </is>
+      </c>
+      <c r="AG47" s="3" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="AH47" s="3" t="inlineStr">
+        <is>
+          <t>郑州经开资本集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+        </is>
+      </c>
+      <c r="AI47" s="3" t="inlineStr">
+        <is>
+          <t>私募</t>
+        </is>
+      </c>
+      <c r="AJ47" s="3" t="inlineStr">
+        <is>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK47" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL47" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO47" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP47" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ47" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>含权</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AZ47" s="3"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/data/credit_bond_all_2026-09-24.xlsx
+++ b/data/credit_bond_all_2026-09-24.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-24" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-25" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-24</t>
+          <t>数据来源：DM    2026-09-25</t>
         </is>
       </c>
     </row>
@@ -713,12 +713,16 @@
       <c r="E3" s="4" t="n">
         <v>20.0</v>
       </c>
-      <c r="F3" s="3"/>
+      <c r="F3" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G3" s="3"/>
       <c r="H3" s="4" t="n">
         <v>1.53</v>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="4" t="n">
+        <v>29.73</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>1.51</t>
@@ -842,7 +846,7 @@
       </c>
       <c r="AM3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN3" s="3" t="inlineStr">
@@ -910,7 +914,7 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26深圳特建MTN001</t>
+          <t>26中广核租SCP007</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -920,60 +924,58 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683829.IB</t>
+          <t>012682359.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>8.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F4" s="3"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.65 ~ 1.95</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>24建工02</t>
+          <t>26中广核租SCP004(绿色)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>2.46Y</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.7921</t>
+          <t>1.5380</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>深圳市特区建工集团有限公司</t>
+          <t>中广核国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>B- 42.38</t>
+          <t>C- 20.83</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -983,12 +985,12 @@
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -996,28 +998,28 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>广东省-深圳市</t>
@@ -1025,23 +1027,23 @@
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据募集资金8亿元,拟用于偿还银行借款</t>
+          <t>本期债务融资工具募集资金5亿元,拟用于偿还即将到期的债务融资工具[26中广核租SCP001]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
@@ -1051,7 +1053,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>深圳市特区建工集团有限公司2026年度第一期中期票据</t>
+          <t>中广核国际融资租赁有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1061,7 +1063,7 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK4" s="3"/>
@@ -1082,32 +1084,32 @@
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1140,45 +1142,53 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26重庆银行债01</t>
+          <t>26中广核租SCP006</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
-        </is>
-      </c>
-      <c r="C5" s="3"/>
+          <t>09-24 18:00</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>012682355.IB</t>
+        </is>
+      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>1.35 ~ 1.55</t>
+        </is>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26重庆银行小微债01(柜台)</t>
+          <t>26中广核租SCP004(绿色)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.5952</t>
+          <t>1.5380</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1188,12 +1198,12 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司</t>
+          <t>中广核国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>A- 67.68</t>
+          <t>C- 20.83</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1203,7 +1213,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:30</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1220,40 +1230,44 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展</t>
-        </is>
-      </c>
-      <c r="AC5" s="3"/>
+          <t>本期债务融资工具募集资金5亿元,拟用于偿还到期银行借款</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>上海银行股份有限公司,浙商银行股份有限公司</t>
+        </is>
+      </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
@@ -1263,7 +1277,7 @@
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司2026年第一期金融债券</t>
+          <t>中广核国际融资租赁有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
@@ -1273,18 +1287,18 @@
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN5" s="3" t="inlineStr">
@@ -1299,27 +1313,27 @@
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1352,7 +1366,7 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26同舟01</t>
+          <t>26国盛MTN004(科创债)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1362,56 +1376,60 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>283936.SH</t>
+          <t>102683834.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3+3+4</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>3.5</v>
+        <v>25.0</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.80 ~ 2.10</t>
         </is>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>25中核二二GN001(科创债)</t>
+          <t>26沪盛K1</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>2.24Y+2.00Y</t>
+          <t>9.94Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.9169</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.9500/1.9000</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P6" s="3"/>
+          <t>上海国盛(集团)有限公司</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>B 52.58</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -1419,7 +1437,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1429,19 +1447,23 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="V6" s="4" t="n">
+        <v>1.05</v>
+      </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
@@ -1452,23 +1474,23 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
+          <t>发行人拟发行25亿元科技创新债券,其中3.5亿元用于偿还债务融资工具,21.5亿元将通过基金出资和股权投资等形式用于支持科技创新企业发展[23国盛MTN005]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1478,71 +1500,79 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>上海国盛(集团)有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
-        </is>
-      </c>
-      <c r="AK6" s="3"/>
+          <t>2036-09-28</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO6" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP6" s="3"/>
-      <c r="AQ6" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>市政路桥</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-29</t>
-        </is>
-      </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -1550,7 +1580,7 @@
       </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX6" s="3" t="inlineStr">
@@ -1563,58 +1593,60 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ6" s="3"/>
+      <c r="AZ6" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26安建02</t>
+          <t>26广州产投SCP007</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>284001.SH</t>
+          <t>012682352.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.6</v>
+        <v>8.1</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.32 ~ 1.52</t>
         </is>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26安建01</t>
+          <t>26广州产投SCP006</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.9446</t>
+          <t>1.5111</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1624,12 +1656,12 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>浙江安吉建设控股集团有限公司</t>
+          <t>广州产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>D- 0.72</t>
+          <t>C 28.72</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1639,56 +1671,60 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V7" s="4" t="n">
+        <v>5.33</v>
+      </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券计划募集资金为5.6亿元,扣除发行费用后,拟全部用于偿还发行人赎回的公司债券本金。[23安建02]</t>
+          <t>本期超短期融资券的发行规模为8.1亿元，募集资金全部用于偿还到期债务融资工具[26广州产投SCP001]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司,国金证券股份有限公司,浙商证券股份有限公司</t>
+          <t>中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
@@ -1698,28 +1734,28 @@
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>浙江安吉建设控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>广州产业投资控股集团有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -1729,37 +1765,37 @@
       </c>
       <c r="AN7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1792,7 +1828,7 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26中广核租SCP007</t>
+          <t>26大唐集SCP018</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1802,43 +1838,43 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>012682359.IB</t>
+          <t>012682354.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.08Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.20 ~ 1.48</t>
         </is>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26中广核租SCP004(绿色)</t>
+          <t>25大唐K1</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>37D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5380</t>
+          <t>1.4784</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1848,12 +1884,12 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>中广核国际融资租赁有限公司</t>
+          <t>中国大唐集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>C- 20.83</t>
+          <t>B- 43.36</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1863,7 +1899,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1877,36 +1913,38 @@
         </is>
       </c>
       <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="V8" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.45%~1.49%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>河北省-保定市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金5亿元,拟用于偿还即将到期的债务融资工具[26中广核租SCP001]</t>
+          <t>本期债务融资工具发行规模为20亿元,拟全部用于偿还有息债务及补充流动资金</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
@@ -1917,7 +1955,7 @@
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
@@ -1927,7 +1965,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>中广核国际融资租赁有限公司2026年度第七期超短期融资券</t>
+          <t>中国大唐集团有限公司2026年度第十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1937,7 +1975,7 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
@@ -1958,32 +1996,32 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>火电</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2016,7 +2054,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26中广核租SCP006</t>
+          <t>26皖国资MTN004(科创债)</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2026,58 +2064,58 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>012682355.IB</t>
+          <t>102683839.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26中广核租SCP004(绿色)</t>
+          <t>26皖国资MTN003</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>2.87Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.5380</t>
+          <t>1.6623</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6850/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>中广核国际融资租赁有限公司</t>
+          <t>安徽省国有资本运营控股集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C- 20.83</t>
+          <t>B- 42.80</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2092,7 +2130,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2104,44 +2142,44 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金5亿元,拟用于偿还到期银行借款</t>
+          <t>本期科技创新债券基础发行金额0亿元,本期发行金额上限6亿元,全部用于置换发行人一年内以股权投资形式对科技创新领域的资金投入。</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,浙商银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG9" s="3" t="inlineStr">
@@ -2151,7 +2189,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>中广核国际融资租赁有限公司2026年度第六期超短期融资券</t>
+          <t>安徽省国有资本运营控股集团有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2161,10 +2199,14 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK9" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK9" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL9" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2182,7 +2224,7 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
@@ -2192,22 +2234,22 @@
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2240,7 +2282,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26国盛MTN004(科创债)</t>
+          <t>26嘉秀发展MTN004</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2250,58 +2292,58 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683834.IB</t>
+          <t>102683833.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>25.0</v>
+        <v>5.1</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26沪盛K1</t>
+          <t>26嘉秀发展MTN003</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>9.94Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.9285</t>
+          <t>1.7867</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>1.9225/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司</t>
+          <t>嘉兴市嘉秀发展投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>B- 46.32</t>
+          <t>C 27.59</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2316,7 +2358,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2324,37 +2366,41 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.27</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人拟发行25亿元科技创新债券,其中3.5亿元用于偿还债务融资工具,21.5亿元将通过基金出资和股权投资等形式用于支持科技创新企业发展[23国盛MTN005]</t>
+          <t>发行人本次中期票据发行金额5.10亿元,拟用于偿还发行人有息债务本金[23嘉秀发展PPN003]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>杭州银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2375,7 +2421,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司2026年度第四期科技创新债券</t>
+          <t>嘉兴市嘉秀发展投资控股集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2385,7 +2431,7 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2036-09-28</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK10" s="3" t="inlineStr">
@@ -2410,32 +2456,32 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2463,14 +2509,12 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ10" s="3"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP007</t>
+          <t>26南电GN008(科创债)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2480,58 +2524,58 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>012682352.IB</t>
+          <t>132680099.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>8.1</v>
+        <v>20.0</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.52</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP006</t>
+          <t>26南电GN007(科创债)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.5111</t>
+          <t>1.6296</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司</t>
+          <t>中国南方电网有限责任公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C 29.22</t>
+          <t>B- 40.65</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2546,7 +2590,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2554,16 +2598,20 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
+      <c r="U11" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2579,23 +2627,23 @@
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券的发行规模为8.1亿元，募集资金全部用于偿还到期债务融资工具[26广州产投SCP001]</t>
+          <t>本期绿色科技创新债券发行规模20亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营以及充电站项目建设</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司</t>
+          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2605,7 +2653,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司2026年度第七期超短期融资券</t>
+          <t>中国南方电网有限责任公司2026年度第八期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2615,7 +2663,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
+          <t>2031-09-22</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2641,27 +2689,27 @@
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2694,7 +2742,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26大唐集SCP018</t>
+          <t>26环球天津SCP005</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2704,58 +2752,58 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>012682354.IB</t>
+          <t>012682360.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.08Y</t>
+          <t>0.47Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.48</t>
+          <t>1.32 ~ 1.62</t>
         </is>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>25大唐K1</t>
+          <t>26环球天津SCP003</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>37D</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.4732</t>
+          <t>1.6380</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/1.4600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>中国大唐集团有限公司</t>
+          <t>通用环球国际融资租赁(天津)有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 42.21</t>
+          <t>C- 10.79</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2782,12 +2830,12 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.45%~1.49%</t>
+          <t>1.63%~1.67%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2798,17 +2846,17 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>河北省-保定市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为20亿元,拟全部用于偿还有息债务及补充流动资金</t>
+          <t>本期超短期融资券发行金额为5亿元,用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>渤海银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2819,7 +2867,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
@@ -2829,7 +2877,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>中国大唐集团有限公司2026年度第十八期超短期融资券</t>
+          <t>通用环球国际融资租赁(天津)有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2839,7 +2887,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2027-03-19</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2860,32 +2908,32 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>火电</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2913,12 +2961,14 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ12" s="3"/>
+      <c r="AZ12" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26皖国资MTN004(科创债)</t>
+          <t>26京国资SCP001</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2928,58 +2978,58 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>102683839.IB</t>
+          <t>012682356.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.0</v>
+        <v>10.0</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26皖国资MTN003</t>
+          <t>24国管01</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.87Y</t>
+          <t>330D</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.6623</t>
+          <t>1.4873</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.6700/--</t>
+          <t>1.5200/1.5100</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>安徽省国有资本运营控股集团有限公司</t>
+          <t>北京国有资本运营管理有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 45.37</t>
+          <t>B- 36.00</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2989,12 +3039,12 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
@@ -3006,12 +3056,12 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3019,26 +3069,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z13" s="3"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券基础发行金额0亿元,本期发行金额上限6亿元,全部用于置换发行人一年内以股权投资形式对科技创新领域的资金投入。</t>
+          <t>本期债务融资工具发行规模为人民币10亿元，发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3053,7 +3107,7 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>安徽省国有资本运营控股集团有限公司2026年度第四期科技创新债券</t>
+          <t>北京国有资本运营管理有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
@@ -3063,14 +3117,10 @@
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-25</t>
+        </is>
+      </c>
+      <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3088,12 +3138,12 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
@@ -3103,12 +3153,12 @@
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
@@ -3146,7 +3196,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26嘉秀发展MTN004</t>
+          <t>26衢产PPN001</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3154,18 +3204,14 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>102683833.IB</t>
-        </is>
-      </c>
+      <c r="C14" s="3"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.1</v>
+        <v>5.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
@@ -3182,32 +3228,32 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26嘉秀发展MTN003</t>
+          <t>26衢产02</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.67Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7867</t>
+          <t>1.7084</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.7600</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市嘉秀发展投资控股集团有限公司</t>
+          <t>衢州市产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 25.65</t>
+          <t>B- 38.75</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3217,7 +3263,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 10:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3227,46 +3273,48 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U14" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>4.54</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>浙江省-衢州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额5.10亿元,拟用于偿还发行人有息债务本金[23嘉秀发展PPN003]</t>
+          <t>本期发行人发行的定向债务融资工具基础发行规模为0亿元,发行金额上限为5亿元,募集资金拟全部用于偿还公司银行贷款。[23衢州控股PPN001]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,杭州银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,恒丰银行股份有限公司,财通证券股份有限公司,上海银行股份有限公司,中信银行股份有限公司,宁波银行股份有限公司,中国建设银行股份有限公司,上海浦东发展银行股份有限公司,浙商银行股份有限公司,南京银行股份有限公司,徽商银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
@@ -3281,67 +3329,67 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市嘉秀发展投资控股集团有限公司2026年度第四期中期票据</t>
+          <t>衢州市产业投资控股集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AK14" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休9</t>
         </is>
       </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3374,7 +3422,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26南电GN008(科创债)</t>
+          <t>26润业投资PPN002B</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3382,60 +3430,56 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>132680099.IB</t>
-        </is>
-      </c>
+      <c r="C15" s="3"/>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>20.0</v>
+        <v>2.5</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26南电GN007(科创债)</t>
+          <t>26润业01</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>2.52Y+2.00Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.6296</t>
+          <t>1.8450</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>1.8900/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司</t>
+          <t>河源市润业投资有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B- 38.72</t>
+          <t>C- 15.95</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3445,12 +3489,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3458,48 +3502,50 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U15" s="3"/>
+      <c r="U15" s="4" t="n">
+        <v>3.05</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>广东省-河源市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模20亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营以及充电站项目建设</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
@@ -3509,20 +3555,24 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司2026年度第八期绿色科技创新债券</t>
+          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种二)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
-        </is>
-      </c>
-      <c r="AK15" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3540,32 +3590,32 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8.5*无效</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3598,7 +3648,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26环球天津SCP005</t>
+          <t>26海螺集团MTN002(科创债/并购)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3608,43 +3658,43 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>012682360.IB</t>
+          <t>102683838.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.47Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.62</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26环球天津SCP003</t>
+          <t>26海螺集团MTN001(科创债)</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.6380</t>
+          <t>1.7555</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -3654,12 +3704,12 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>通用环球国际融资租赁(天津)有限公司</t>
+          <t>安徽海螺集团有限责任公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 10.79</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3674,7 +3724,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3682,16 +3732,20 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>1.28</v>
+      </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.67%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3702,28 +3756,28 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为5亿元,用于偿还发行人存量有息债务</t>
+          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3733,7 +3787,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>通用环球国际融资租赁(天津)有限公司2026年度第五期超短期融资券</t>
+          <t>安徽海螺集团有限责任公司2026年度第二期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3743,10 +3797,14 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2027-03-19</t>
-        </is>
-      </c>
-      <c r="AK16" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3764,32 +3822,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3817,14 +3875,12 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26京国资SCP001</t>
+          <t>26夏商SCP028</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3834,21 +3890,21 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>012682356.IB</t>
+          <t>012682357.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>0.22Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.21 ~ 1.51</t>
         </is>
       </c>
       <c r="H17" s="3"/>
@@ -3860,32 +3916,32 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>24国管01</t>
+          <t>26夏商SCP026</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>330D</t>
+          <t>78D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.4842</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5100</t>
+          <t>1.5200/1.4900</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 37.61</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3895,7 +3951,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3912,7 +3968,7 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
@@ -3922,27 +3978,23 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z17" s="3" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币10亿元，发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
+          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于用于补充发行人子公司厦门夏商民昇贸易有限公司营运资金。</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -3963,7 +4015,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司2026年度第一期超短期融资券</t>
+          <t>厦门夏商集团有限公司2026年度第二十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -3973,10 +4025,14 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2026-12-19</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3999,27 +4055,27 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4047,73 +4103,75 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP028</t>
+          <t>26宁德时代MTN008B(科创债)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 18:30</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>012682357.IB</t>
+          <t>102683832.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>0.22Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.21 ~ 1.51</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP026</t>
+          <t>26宁德时代MTN007B(科创债)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>78D</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.7410</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.4900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>宁德时代新能源科技股份有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 49.30</t>
+          <t>B- 38.15</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4140,44 +4198,44 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>福建省-宁德市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于用于补充发行人子公司厦门夏商民昇贸易有限公司营运资金。</t>
+          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG18" s="3" t="inlineStr">
@@ -4187,7 +4245,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十八期超短期融资券</t>
+          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种二)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4197,12 +4255,12 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK18" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL18" s="3" t="inlineStr">
@@ -4212,7 +4270,7 @@
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN18" s="3" t="inlineStr">
@@ -4227,27 +4285,27 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>电源设备</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4275,71 +4333,73 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ18" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ18" s="3"/>
     </row>
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26衢产PPN001</t>
+          <t>26宁德时代MTN008A(科创债)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
-        </is>
-      </c>
-      <c r="C19" s="3"/>
+          <t>09-24 18:30</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>102683831.IB</t>
+        </is>
+      </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26衢产02</t>
+          <t>26宁德时代MTN007A(科创债)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.67Y</t>
+          <t>2.99Y+2.00Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.7164</t>
+          <t>1.6700</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/1.7100</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>衢州市产业投资控股集团有限公司</t>
+          <t>宁德时代新能源科技股份有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 38.13</t>
+          <t>B- 38.15</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4349,7 +4409,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-24 10:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4359,19 +4419,19 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4382,28 +4442,28 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>浙江省-衢州市</t>
+          <t>福建省-宁德市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期发行人发行的定向债务融资工具基础发行规模为0亿元,发行金额上限为5亿元,募集资金拟全部用于偿还公司银行贷款。[23衢州控股PPN001]</t>
+          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,杭州银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,恒丰银行股份有限公司,财通证券股份有限公司,上海银行股份有限公司,中信银行股份有限公司,宁波银行股份有限公司,中国建设银行股份有限公司,上海浦东发展银行股份有限公司,浙商银行股份有限公司,南京银行股份有限公司,徽商银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
@@ -4413,37 +4473,37 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>衢州市产业投资控股集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种一)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK19" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
@@ -4453,32 +4513,32 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电源设备</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV19" s="3" t="inlineStr">
@@ -4488,7 +4548,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4506,64 +4566,72 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26润业投资PPN002B</t>
+          <t>26柯桥03</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
-        </is>
-      </c>
-      <c r="C20" s="3"/>
+          <t>09-24 19:00</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>284145.SH</t>
+        </is>
+      </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.5</v>
+        <v>20.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>43.88</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26润业01</t>
+          <t>26绍兴柯桥PPN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.52Y+2.00Y</t>
+          <t>4.44Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.8400</t>
+          <t>1.9325</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.8900/--</t>
+          <t>1.9700/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司</t>
+          <t>绍兴市柯桥区建设集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C- 15.95</t>
+          <t>C 28.59</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4590,12 +4658,12 @@
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4606,23 +4674,23 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>广东省-河源市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23柯桥01]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
       <c r="AE20" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF20" s="3" t="inlineStr">
@@ -4632,12 +4700,12 @@
       </c>
       <c r="AG20" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种二)</t>
+          <t>绍兴市柯桥区建设集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4647,64 +4715,60 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
+          <t>2033-09-28</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
           <t>2031-09-28</t>
         </is>
       </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AM20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO20" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>8.5*无效</t>
-        </is>
-      </c>
-      <c r="AQ20" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR20" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS20" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT20" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU20" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4712,7 +4776,7 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4730,22 +4794,22 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN002(科创债/并购)</t>
+          <t>26方大01</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>102683838.IB</t>
+          <t>284123.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
@@ -4754,44 +4818,48 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+          <t>4.30 ~ 6.30</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>421.07</v>
+      </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN001(科创债)</t>
+          <t>24辽宁方大MTN001</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>218D</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7555</t>
+          <t>5.9380</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/5.5000</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司</t>
+          <t>辽宁方大集团实业有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>A 80.00</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4801,7 +4869,7 @@
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
@@ -4811,93 +4879,89 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t>1.72%~1.82%</t>
-        </is>
-      </c>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X21" s="3"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
+          <t>本期债券发行规模为不超过人民币10.00亿元(含10.00亿元),债券募集资金扣除发行费用后,拟全部用于偿还到期的有息债务。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司2026年度第二期科技创新债券(并购)</t>
+          <t>辽宁方大集团实业有限公司2026年面向专业投资者非公开发行公司债券(高成长产业债)(第一期)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AK21" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休9</t>
         </is>
       </c>
       <c r="AL21" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -4905,32 +4969,32 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="AV21" s="3" t="inlineStr">
@@ -4940,7 +5004,7 @@
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -4958,53 +5022,53 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN008B(科创债)</t>
+          <t>26同舟02</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>102683832.IB</t>
+          <t>283937.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>25.0</v>
+        <v>3.5</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.80 ~ 2.40</t>
         </is>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN007B(科创债)</t>
+          <t>25中核二二GN001(科创债)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>2.24Y+2.00Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.7410</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5014,14 +5078,10 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t>B- 40.04</t>
-        </is>
-      </c>
+          <t>山东同舟产业控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P22" s="3"/>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -5029,7 +5089,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
@@ -5039,19 +5099,19 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>2.30%~2.40%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5062,103 +5122,95 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>福建省-宁德市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
+          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种二)</t>
+          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK22" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2036-09-29</t>
+        </is>
+      </c>
+      <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP22" s="3"/>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>电源设备</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV22" s="3" t="inlineStr">
@@ -5168,7 +5220,7 @@
       </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr">
@@ -5186,70 +5238,66 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26句容03</t>
+          <t>26同舟01</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>283950.SH</t>
+          <t>283936.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+3+4</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>9.0</v>
+        <v>3.5</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>26句容01</t>
+          <t>25中核二二GN001(科创债)</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>4.72Y</t>
+          <t>2.24Y+2.00Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.0026</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>2.1000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>江苏句容福地生态科技有限公司</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>B- 35.73</t>
-        </is>
-      </c>
+          <t>山东同舟产业控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P23" s="3"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -5267,40 +5315,40 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将9.00亿元用于偿还回售的公司债券本金[23句容04]</t>
+          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
+          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5321,7 +5369,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>江苏句容福地生态科技有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5331,14 +5379,10 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK23" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2036-09-29</t>
+        </is>
+      </c>
+      <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5351,42 +5395,38 @@
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP23" s="3"/>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>市政路桥</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR23" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV23" s="3" t="inlineStr">
@@ -5396,7 +5436,7 @@
       </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX23" s="3" t="inlineStr">
@@ -5414,17 +5454,17 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26港兴01</t>
+          <t>26港兴02</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>283963.SH</t>
+          <t>283964.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5433,16 +5473,20 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>71.42</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -5490,7 +5534,11 @@
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -5509,7 +5557,7 @@
       </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>江苏省信用增进有限责任公司</t>
+          <t>湖南财鑫融资担保有限公司</t>
         </is>
       </c>
       <c r="AE24" s="3" t="inlineStr">
@@ -5529,7 +5577,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5618,17 +5666,17 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26港兴02</t>
+          <t>26港兴01</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>283964.SH</t>
+          <t>283963.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5637,16 +5685,20 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>61.42</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -5694,7 +5746,11 @@
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -5713,7 +5769,7 @@
       </c>
       <c r="AD25" s="3" t="inlineStr">
         <is>
-          <t>湖南财鑫融资担保有限公司</t>
+          <t>江苏省信用增进有限责任公司</t>
         </is>
       </c>
       <c r="AE25" s="3" t="inlineStr">
@@ -5733,7 +5789,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5822,68 +5878,72 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26方大01</t>
+          <t>26郑经K1</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>284123.SH</t>
+          <t>284034.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>2+1</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>4.30 ~ 6.30</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>39.42</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24辽宁方大MTN001</t>
+          <t>26郑经01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>218D</t>
+          <t>2.31Y+2.00Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>5.9380</t>
+          <t>1.6852</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>6.0000/5.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>辽宁方大集团实业有限公司</t>
+          <t>郑州经开资本集团有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>D+ 10.00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5893,7 +5953,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 16:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -5903,7 +5963,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U26" s="3"/>
@@ -5922,17 +5982,17 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币10.00亿元(含10.00亿元),债券募集资金扣除发行费用后,拟全部用于偿还到期的有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不低于0.70亿元募集资金通过发行人本部或子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余资金用于偿还有息负债。</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司</t>
+          <t>申万宏源证券有限公司,东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -5943,7 +6003,7 @@
       </c>
       <c r="AF26" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG26" s="3" t="inlineStr">
@@ -5953,7 +6013,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>辽宁方大集团实业有限公司2026年面向专业投资者非公开发行公司债券(高成长产业债)(第一期)</t>
+          <t>郑州经开资本集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -5963,12 +6023,12 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK26" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL26" s="3" t="inlineStr">
@@ -5983,42 +6043,42 @@
       </c>
       <c r="AN26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
       <c r="AU26" s="3" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV26" s="3" t="inlineStr">
@@ -6046,68 +6106,72 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26郑州交发MTN002(绿色)</t>
+          <t>26澄港01</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102683830.IB</t>
+          <t>525027.SZ</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>40.42</v>
+      </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24郑州地铁GN002</t>
+          <t>24江阴临港MTN001</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>1.12Y+N</t>
+          <t>1.14Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6185</t>
+          <t>1.5659</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司</t>
+          <t>江阴临港新城开发建设有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C- 20.57</t>
+          <t>C+ 32.94</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6117,7 +6181,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 16:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6127,46 +6191,46 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t>1.71%~1.81%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X27" s="3"/>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额上限10.00亿元,基础发行规模0亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
+          <t>本期债券发行总额不超过8.00亿元,公司仅可将本期债券募集资金用于偿还到期公司债券本金[21澄港04]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD27" s="3"/>
+          <t>中信证券股份有限公司,东吴证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>中证信用融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
@@ -6176,12 +6240,12 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司2026年度第二期绿色中期票据</t>
+          <t>江阴临港新城开发建设有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6191,33 +6255,33 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6227,17 +6291,17 @@
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6247,17 +6311,17 @@
       </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY27" s="3" t="inlineStr">
@@ -6270,51 +6334,57 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26浙商证券CP006</t>
+          <t>26安建02</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:30</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>072610196.IB</t>
+          <t>284001.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>0.66Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>15.0</v>
+        <v>5.6</v>
       </c>
       <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
       <c r="H28" s="4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="I28" s="3"/>
+        <v>1.98</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>57.42</v>
+      </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26浙商证券CP005</t>
+          <t>26安建01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>274D</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.5251</t>
+          <t>1.9314</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6324,12 +6394,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>浙江安吉建设控股集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>B- 36.94</t>
+          <t>D- 0.72</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6339,7 +6409,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6349,42 +6419,46 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.93%~2.03%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
-        </is>
-      </c>
-      <c r="AB28" s="3"/>
+          <t>浙江省-湖州市</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券计划募集资金为5.6亿元,扣除发行费用后,拟全部用于偿还发行人赎回的公司债券本金。[23安建02]</t>
+        </is>
+      </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>财通证券股份有限公司,国金证券股份有限公司,浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6394,68 +6468,68 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司2026年度第六期短期融资券</t>
+          <t>浙江安吉建设控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2027-05-26</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
@@ -6488,66 +6562,72 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP010</t>
+          <t>26惠鑫01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>072610197.IB</t>
+          <t>284108.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0.91Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>40.0</v>
+        <v>7.57</v>
       </c>
       <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
       <c r="H29" s="4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="I29" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>59.42</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP006</t>
+          <t>25惠鑫01</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>264D</t>
+          <t>3.66Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.4951</t>
+          <t>1.8229</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.5200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>无锡惠鑫汇资产经营管理有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>A- 68.49</t>
+          <t>D- 0.72</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6557,7 +6637,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6567,42 +6647,46 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB29" s="3"/>
+          <t>江苏省-无锡市</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>本期债券拟将募集资金7.57亿元用于偿还到期公司债券本金[24惠鑫01,23惠鑫04]</t>
+        </is>
+      </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>东吴证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6612,68 +6696,68 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第十期短期融资券</t>
+          <t>无锡惠鑫汇资产经营管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6706,53 +6790,57 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26锡铁01</t>
+          <t>26柯资03</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 18:30</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>284118.SH</t>
+          <t>284115.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>41.07</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26锡铁D1</t>
+          <t>26柯资02</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>315D</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.5279</t>
+          <t>1.6910</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
@@ -6762,12 +6850,12 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>无锡地铁集团有限公司</t>
+          <t>绍兴市柯桥区国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C- 25.00</t>
+          <t>C+ 30.27</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6794,33 +6882,33 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于置换自有资金偿还的公司债券本金[GY锡铁01]</t>
+          <t>本期债券发行规模为不超过10亿元(含10亿元),募集资金拟全部用于偿还到期公司债券的本金。[23柯资05,23柯资06]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -6841,7 +6929,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>无锡地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>绍兴市柯桥区国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -6851,14 +6939,10 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK30" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6866,7 +6950,7 @@
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -6876,32 +6960,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -6934,66 +7018,74 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26同舟02</t>
+          <t>26句容03</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283937.SH</t>
+          <t>283950.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.5</v>
+        <v>9.0</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>59.42</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>25中核二二GN001(科创债)</t>
+          <t>26句容01</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>2.24Y+2.00Y</t>
+          <t>4.72Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.9886</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1000/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P31" s="3"/>
+          <t>江苏句容福地生态科技有限公司</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>B- 35.73</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -7011,40 +7103,40 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>2.30%~2.40%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将9.00亿元用于偿还回售的公司债券本金[23句容04]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7065,7 +7157,7 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>江苏句容福地生态科技有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
@@ -7075,10 +7167,14 @@
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
-        </is>
-      </c>
-      <c r="AK31" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK31" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL31" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7091,38 +7187,42 @@
       </c>
       <c r="AN31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP31" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV31" s="3" t="inlineStr">
@@ -7132,7 +7232,7 @@
       </c>
       <c r="AW31" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX31" s="3" t="inlineStr">
@@ -7150,53 +7250,55 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26中交三航SCP023</t>
+          <t>26浙商证券CP006</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 17:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>012682353.IB</t>
+          <t>072610196.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.66Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>1.30 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+        <v>15.0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="G32" s="3"/>
+      <c r="H32" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>30.72</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>26中交三航SCP019</t>
+          <t>26浙商证券CP005</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>97D</t>
+          <t>274D</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.5002</t>
+          <t>1.5251</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7206,12 +7308,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>中交第三航务工程局有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.09</t>
+          <t>B- 35.25</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7238,12 +7340,12 @@
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7254,28 +7356,24 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB32" s="3" t="inlineStr">
-        <is>
-          <t>本期发行金额为5亿元，全部用于归还发行人本部有息负债</t>
-        </is>
-      </c>
+          <t>浙江省-杭州市</t>
+        </is>
+      </c>
+      <c r="AB32" s="3"/>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,兴业银行股份有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7285,7 +7383,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>中交第三航务工程局有限公司2026年度第二十三期超短期融资券</t>
+          <t>浙商证券股份有限公司2026年度第六期短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7295,7 +7393,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-05-26</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7306,7 +7404,7 @@
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
@@ -7316,32 +7414,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7369,75 +7467,75 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ32" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ32" s="3"/>
     </row>
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN001</t>
+          <t>26国泰海通CP010</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 17:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>102683837.IB</t>
+          <t>072610197.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.91Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>1.20 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+        <v>40.0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>28.99</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>26国泰海通CP006</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.21Y</t>
+          <t>264D</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.6011</t>
+          <t>1.4951</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 49.82</t>
+          <t>A- 68.21</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7464,12 +7562,12 @@
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7483,25 +7581,21 @@
           <t>上海市</t>
         </is>
       </c>
-      <c r="AB33" s="3" t="inlineStr">
-        <is>
-          <t>本期中期票据发行金额为16亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金。</t>
-        </is>
-      </c>
+      <c r="AB33" s="3"/>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7511,7 +7605,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第一期中期票据</t>
+          <t>国泰海通证券股份有限公司2026年度第十期短期融资券</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7521,7 +7615,7 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2027-08-26</t>
         </is>
       </c>
       <c r="AK33" s="3"/>
@@ -7532,7 +7626,7 @@
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
@@ -7542,32 +7636,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7600,7 +7694,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN003(科创债/并购)</t>
+          <t>26中交三航SCP023</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7610,43 +7704,43 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>102683836.IB</t>
+          <t>012682353.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN001(科创债)</t>
+          <t>26中交三航SCP019</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>97D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.7555</t>
+          <t>1.5002</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7656,12 +7750,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司</t>
+          <t>中交第三航务工程局有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>A 80.00</t>
+          <t>C+ 30.74</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7676,7 +7770,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -7684,16 +7778,20 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
+      <c r="U34" s="4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7704,28 +7802,28 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
+          <t>本期发行金额为5亿元，全部用于归还发行人本部有息负债</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
+          <t>广发银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -7735,7 +7833,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司2026年度第三期科技创新债券(并购)</t>
+          <t>中交第三航务工程局有限公司2026年度第二十三期超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7745,14 +7843,10 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK34" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -7775,27 +7869,27 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -7823,12 +7917,14 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ34" s="3"/>
+      <c r="AZ34" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26乌江水电GN005</t>
+          <t>26东航股MTN001</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7838,90 +7934,92 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>132680100.IB</t>
+          <t>102683837.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.65</t>
+          <t>1.20 ~ 1.80</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>25东航股MTN006</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>2.21Y</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>1.6011</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>1.6200/--</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>中国东方航空股份有限公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>B+ 57.72</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>09-24 09:00</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t>26乌江水电GN002</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>179D</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t>1.5294</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t>1.5400/--</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>贵州乌江水电开发有限责任公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>C 26.67</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t>09-24 09:00</t>
-        </is>
-      </c>
-      <c r="S35" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
       <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
+      <c r="V35" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -7932,23 +8030,23 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期绿色超短期融资券发行金额3亿元,募集资金将全部用于偿还构皮滩水电站等6个水电站有息负债本金</t>
+          <t>本期中期票据发行金额为16亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -7963,7 +8061,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江水电开发有限责任公司2026年度第五期绿色超短期融资券</t>
+          <t>中国东方航空股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -7973,7 +8071,7 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
@@ -7999,27 +8097,27 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8052,7 +8150,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26柯资03</t>
+          <t>26海螺集团MTN003(科创债/并购)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8062,12 +8160,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>284115.SH</t>
+          <t>102683836.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -8076,44 +8174,44 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26柯资02</t>
+          <t>26海螺集团MTN001(科创债)</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.6924</t>
+          <t>1.7555</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>1.7300/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区国有资产投资经营集团有限公司</t>
+          <t>安徽海螺集团有限责任公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.01</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8123,12 +8221,12 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8136,43 +8234,47 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
+      <c r="U36" s="4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过10亿元(含10亿元),募集资金拟全部用于偿还到期公司债券的本金。[23柯资05,23柯资06]</t>
+          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8182,28 +8284,32 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>安徽海螺集团有限责任公司2026年度第三期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
-        </is>
-      </c>
-      <c r="AK36" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8218,32 +8324,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8276,68 +8382,68 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26柯桥03</t>
+          <t>26乌江水电GN005</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>284145.SH</t>
+          <t>132680100.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 1.65</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26绍兴柯桥PPN001</t>
+          <t>26乌江水电GN002</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.44Y</t>
+          <t>179D</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.9325</t>
+          <t>1.5294</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.9700/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区建设集团有限公司</t>
+          <t>贵州乌江水电开发有限责任公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C 28.59</t>
+          <t>C+ 30.84</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8347,7 +8453,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -8360,121 +8466,125 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+      <c r="U37" s="4" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>6.5</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23柯桥01]</t>
+          <t>本期绿色超短期融资券发行金额3亿元,募集资金将全部用于偿还构皮滩水电站等6个水电站有息负债本金</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国投证券股份有限公司</t>
+          <t>中国银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区建设集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>贵州乌江水电开发有限责任公司2026年度第五期绿色超短期融资券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2033-09-28</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>水电</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO37" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ37" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR37" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS37" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT37" s="3" t="inlineStr">
-        <is>
-          <t>房屋建设</t>
-        </is>
-      </c>
-      <c r="AU37" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
       <c r="AV37" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8482,7 +8592,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8495,7 +8605,9 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
@@ -8551,7 +8663,7 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.4900</t>
+          <t>1.5200/1.4900</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
@@ -8561,7 +8673,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 49.30</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8770,12 +8882,12 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.4842</t>
+          <t>1.4873</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.5300/1.5100</t>
+          <t>1.5200/1.5100</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -8785,7 +8897,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 37.61</t>
+          <t>B- 36.00</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8800,7 +8912,7 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -8808,7 +8920,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U39" s="3"/>
+      <c r="U39" s="4" t="n">
+        <v>1.2</v>
+      </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
@@ -9003,7 +9117,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6400</t>
+          <t>1.7000/1.6400</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -9013,7 +9127,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 38.74</t>
+          <t>B- 37.26</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9028,7 +9142,7 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -9036,7 +9150,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U40" s="3"/>
+      <c r="U40" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
@@ -9180,68 +9296,64 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26惠鑫01</t>
+          <t>26靖江滨江PPN002</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:30</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>284108.SH</t>
-        </is>
-      </c>
+          <t>09-24 18:00</t>
+        </is>
+      </c>
+      <c r="C41" s="3"/>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>7.57</v>
+        <v>2.5</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.38 ~ 2.10</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>25惠鑫01</t>
+          <t>25靖滨03</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>3.66Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.8399</t>
+          <t>1.6568</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>无锡惠鑫汇资产经营管理有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>D- 0.72</t>
+          <t>C 25.71</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9251,29 +9363,33 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
@@ -9284,23 +9400,23 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟将募集资金7.57亿元用于偿还到期公司债券本金[24惠鑫01,23惠鑫04]</t>
+          <t>本期定向债务融资工具发行金额2.5亿元,用于置换有息债务[26靖江滨江SCP001]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天风证券股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9310,12 +9426,12 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>无锡惠鑫汇资产经营管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>靖江市滨江新城投资开发有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9325,13 +9441,13 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2028-09-28</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM41" s="3" t="inlineStr">
@@ -9341,12 +9457,12 @@
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
@@ -9404,7 +9520,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26靖江滨江PPN002</t>
+          <t>26润业投资PPN002A</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9415,7 +9531,7 @@
       <c r="C42" s="3"/>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -9424,44 +9540,44 @@
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.38 ~ 2.10</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25靖滨03</t>
+          <t>26润业01</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>2.52Y+2.00Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.6599</t>
+          <t>1.8450</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/1.6100</t>
+          <t>1.8900/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>河源市润业投资有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 23.01</t>
+          <t>C- 15.95</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9471,12 +9587,12 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
@@ -9484,37 +9600,39 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U42" s="3"/>
+      <c r="U42" s="4" t="n">
+        <v>2.97</v>
+      </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>广东省-河源市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额2.5亿元,用于置换有息债务[26靖江滨江SCP001]</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
@@ -9535,7 +9653,7 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年度第二期定向债务融资工具</t>
+          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
@@ -9545,10 +9663,14 @@
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2028-09-28</t>
-        </is>
-      </c>
-      <c r="AK42" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK42" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL42" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -9566,12 +9688,12 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.5*无效</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
@@ -9581,12 +9703,12 @@
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
@@ -9596,7 +9718,7 @@
       </c>
       <c r="AU42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV42" s="3" t="inlineStr">
@@ -9606,7 +9728,7 @@
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
@@ -9624,7 +9746,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26润业投资PPN002A</t>
+          <t>26东阳国资PPN002</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9635,11 +9757,11 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
@@ -9656,32 +9778,32 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26润业01</t>
+          <t>26东阳国资PPN001A</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.52Y+2.00Y</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.8400</t>
+          <t>1.8376</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>1.8900/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司</t>
+          <t>东阳市国有资产投资有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 15.95</t>
+          <t>C- 17.96</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9691,12 +9813,12 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
@@ -9708,7 +9830,7 @@
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -9724,17 +9846,17 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>广东省-河源市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
+          <t>发行人本期拟发行规模为人民币5亿元，用于偿还有息负债[23东阳国资PPN003]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
@@ -9755,7 +9877,7 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种一)</t>
+          <t>东阳市国有资产投资有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
@@ -9795,22 +9917,22 @@
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>8.5*无效</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
@@ -9820,7 +9942,7 @@
       </c>
       <c r="AU43" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV43" s="3" t="inlineStr">
@@ -9830,7 +9952,7 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
@@ -9848,7 +9970,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26东阳国资PPN002</t>
+          <t>26深圳特建MTN001</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9856,41 +9978,47 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C44" s="3"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>102683829.IB</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F44" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26东阳国资PPN001A</t>
+          <t>24建工02</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>2.46Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.8376</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -9900,12 +10028,12 @@
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>东阳市国有资产投资有限公司</t>
+          <t>深圳市特区建工集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 17.96</t>
+          <t>B- 42.38</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -9937,34 +10065,38 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z44" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行规模为人民币5亿元，用于偿还有息负债[23东阳国资PPN003]</t>
+          <t>发行人本期中期票据募集资金8亿元,拟用于偿还银行借款</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司</t>
+          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -9979,24 +10111,20 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>东阳市国有资产投资有限公司2026年度第二期定向债务融资工具</t>
+          <t>深圳市特区建工集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK44" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -10014,32 +10142,32 @@
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10072,68 +10200,70 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN008A(科创债)</t>
+          <t>26重庆银行债01</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 17:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>102683831.IB</t>
+          <t>212680058.IB</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="G45" s="3"/>
+      <c r="H45" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>31.07</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN007A(科创债)</t>
+          <t>26重庆银行小微债01(柜台)</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.99Y+2.00Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.6700</t>
+          <t>1.5952</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>1.6900/1.6700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司</t>
+          <t>重庆银行股份有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>B- 40.04</t>
+          <t>A 71.85</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10143,7 +10273,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 09:30</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10160,12 +10290,12 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10176,28 +10306,24 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>福建省-宁德市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
-        </is>
-      </c>
-      <c r="AC45" s="3" t="inlineStr">
-        <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展</t>
+        </is>
+      </c>
+      <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
@@ -10207,7 +10333,7 @@
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种一)</t>
+          <t>重庆银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10217,22 +10343,18 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK45" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK45" s="3"/>
       <c r="AL45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
@@ -10242,37 +10364,37 @@
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>电源设备</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
@@ -10282,7 +10404,7 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -10300,7 +10422,7 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26澄港01</t>
+          <t>26郑州交发MTN002(绿色)</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -10310,58 +10432,58 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>525027.SZ</t>
+          <t>102683830.IB</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>24江阴临港MTN001</t>
+          <t>24郑州地铁GN002</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1.14Y</t>
+          <t>1.12Y+N</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.5659</t>
+          <t>1.6185</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>江阴临港新城开发建设有限公司</t>
+          <t>郑州交通发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.94</t>
+          <t>C- 16.21</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10371,56 +10493,60 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-24 16:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="V46" s="4" t="n">
+        <v>9.0</v>
+      </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X46" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过8.00亿元,公司仅可将本期债券募集资金用于偿还到期公司债券本金[21澄港04]</t>
+          <t>本期发行金额上限10.00亿元,基础发行规模0亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD46" s="3" t="inlineStr">
-        <is>
-          <t>中证信用融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
@@ -10430,12 +10556,12 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>江阴临港新城开发建设有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>郑州交通发展投资集团有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
@@ -10445,73 +10571,73 @@
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO46" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP46" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ46" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>轨道交通</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>铁路运输</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO46" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP46" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ46" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR46" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS46" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT46" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU46" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV46" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY46" s="3" t="inlineStr">
@@ -10524,7 +10650,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26郑经K1</t>
+          <t>26锡铁01</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10534,58 +10660,62 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>284034.SH</t>
+          <t>284118.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>44.42</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26郑经01</t>
+          <t>26锡铁D1</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.31Y+2.00Y</t>
+          <t>315D</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.7867</t>
+          <t>1.5157</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>1.8200/1.6600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>郑州经开资本集团有限公司</t>
+          <t>无锡地铁集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>C- 25.00</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10595,7 +10725,7 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-24 16:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -10612,29 +10742,33 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X47" s="3"/>
+          <t>4+</t>
+        </is>
+      </c>
+      <c r="X47" s="3" t="inlineStr">
+        <is>
+          <t>1.74%~1.84%</t>
+        </is>
+      </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不低于0.70亿元募集资金通过发行人本部或子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余资金用于偿还有息负债。</t>
+          <t>本期债券募集资金拟全部用于置换自有资金偿还的公司债券本金[GY锡铁01]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,东兴证券股份有限公司</t>
+          <t>天风证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10655,7 +10789,7 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>郑州经开资本集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>无锡地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
@@ -10680,7 +10814,7 @@
       </c>
       <c r="AM47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN47" s="3" t="inlineStr">
@@ -10695,7 +10829,7 @@
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
@@ -10705,22 +10839,22 @@
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV47" s="3" t="inlineStr">
@@ -10730,7 +10864,7 @@
       </c>
       <c r="AW47" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX47" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-24.xlsx
+++ b/data/credit_bond_all_2026-09-24.xlsx
@@ -935,7 +935,9 @@
       <c r="E4" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>1.35 ~ 1.55</t>
@@ -1163,7 +1165,9 @@
       <c r="E5" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.35 ~ 1.55</t>
@@ -1387,7 +1391,9 @@
       <c r="E6" s="4" t="n">
         <v>25.0</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>25.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.10</t>
@@ -1621,7 +1627,9 @@
       <c r="E7" s="4" t="n">
         <v>8.1</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="n">
+        <v>8.1</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>1.32 ~ 1.52</t>
@@ -1849,7 +1857,9 @@
       <c r="E8" s="4" t="n">
         <v>20.0</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 1.48</t>
@@ -2075,7 +2085,9 @@
       <c r="E9" s="4" t="n">
         <v>6.0</v>
       </c>
-      <c r="F9" s="3"/>
+      <c r="F9" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.20</t>
@@ -2303,7 +2315,9 @@
       <c r="E10" s="4" t="n">
         <v>5.1</v>
       </c>
-      <c r="F10" s="3"/>
+      <c r="F10" s="4" t="n">
+        <v>5.1</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 2.40</t>
@@ -2535,7 +2549,9 @@
       <c r="E11" s="4" t="n">
         <v>20.0</v>
       </c>
-      <c r="F11" s="3"/>
+      <c r="F11" s="4" t="n">
+        <v>20.0</v>
+      </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 1.90</t>
@@ -2763,7 +2779,9 @@
       <c r="E12" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F12" s="3"/>
+      <c r="F12" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
           <t>1.32 ~ 1.62</t>
@@ -2989,7 +3007,9 @@
       <c r="E13" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F13" s="3"/>
+      <c r="F13" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.50</t>
@@ -3669,7 +3689,9 @@
       <c r="E16" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.10</t>
@@ -3901,7 +3923,9 @@
       <c r="E17" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F17" s="3"/>
+      <c r="F17" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
           <t>1.21 ~ 1.51</t>
@@ -4131,7 +4155,9 @@
       <c r="E18" s="4" t="n">
         <v>25.0</v>
       </c>
-      <c r="F18" s="3"/>
+      <c r="F18" s="4" t="n">
+        <v>25.0</v>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.10</t>
@@ -4359,7 +4385,9 @@
       <c r="E19" s="4" t="n">
         <v>25.0</v>
       </c>
-      <c r="F19" s="3"/>
+      <c r="F19" s="4" t="n">
+        <v>25.0</v>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 2.00</t>
@@ -7715,7 +7743,9 @@
       <c r="E34" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F34" s="3"/>
+      <c r="F34" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.50</t>
@@ -7945,7 +7975,9 @@
       <c r="E35" s="4" t="n">
         <v>16.0</v>
       </c>
-      <c r="F35" s="3"/>
+      <c r="F35" s="4" t="n">
+        <v>16.0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
           <t>1.20 ~ 1.80</t>
@@ -8171,7 +8203,9 @@
       <c r="E36" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F36" s="3"/>
+      <c r="F36" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
           <t>1.50 ~ 2.10</t>
@@ -8403,7 +8437,9 @@
       <c r="E37" s="4" t="n">
         <v>3.0</v>
       </c>
-      <c r="F37" s="3"/>
+      <c r="F37" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 1.65</t>
@@ -8633,7 +8669,9 @@
       <c r="E38" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F38" s="3"/>
+      <c r="F38" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 1.51</t>
@@ -8857,7 +8895,9 @@
       <c r="E39" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F39" s="3"/>
+      <c r="F39" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.50</t>
@@ -9087,7 +9127,9 @@
       <c r="E40" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F40" s="3"/>
+      <c r="F40" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 2.40</t>
@@ -10443,7 +10485,9 @@
       <c r="E46" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F46" s="3"/>
+      <c r="F46" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
           <t>1.40 ~ 2.00</t>

--- a/data/credit_bond_all_2026-09-24.xlsx
+++ b/data/credit_bond_all_2026-09-24.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-25" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-25</t>
+          <t>数据来源：DM    2026-09-28</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4450,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>1.43</v>
+      </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>

--- a/data/credit_bond_all_2026-09-24.xlsx
+++ b/data/credit_bond_all_2026-09-24.xlsx
@@ -943,8 +943,12 @@
           <t>1.35 ~ 1.55</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>18.72</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.49</t>
@@ -1173,8 +1177,12 @@
           <t>1.35 ~ 1.55</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>18.72</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.49</t>
@@ -1399,8 +1407,12 @@
           <t>1.80 ~ 2.10</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>19.62</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.92</t>
@@ -1635,8 +1647,12 @@
           <t>1.32 ~ 1.52</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>25.72</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.50</t>
@@ -1865,8 +1881,12 @@
           <t>1.20 ~ 1.48</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>16.33</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>1.44</t>
@@ -1922,7 +1942,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>1.025</v>
+      </c>
       <c r="V8" s="4" t="n">
         <v>1.0</v>
       </c>
@@ -2064,7 +2086,7 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26皖国资MTN004(科创债)</t>
+          <t>26嘉秀发展MTN004</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2074,7 +2096,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683839.IB</t>
+          <t>102683833.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2083,51 +2105,55 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.0</v>
+        <v>5.1</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>6.0</v>
+        <v>5.1</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>27.42</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26皖国资MTN003</t>
+          <t>26嘉秀发展MTN003</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>2.87Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6623</t>
+          <t>1.7867</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.6850/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>安徽省国有资本运营控股集团有限公司</t>
+          <t>嘉兴市嘉秀发展投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>B- 42.80</t>
+          <t>C 27.59</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2142,7 +2168,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -2150,37 +2176,41 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="V9" s="4" t="n">
+        <v>1.27</v>
+      </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券基础发行金额0亿元,本期发行金额上限6亿元,全部用于置换发行人一年内以股权投资形式对科技创新领域的资金投入。</t>
+          <t>发行人本次中期票据发行金额5.10亿元,拟用于偿还发行人有息债务本金[23嘉秀发展PPN003]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>杭州银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
@@ -2201,7 +2231,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>安徽省国有资本运营控股集团有限公司2026年度第四期科技创新债券</t>
+          <t>嘉兴市嘉秀发展投资控股集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2236,32 +2266,32 @@
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2294,7 +2324,7 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26嘉秀发展MTN004</t>
+          <t>26南电GN008(科创债)</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2304,60 +2334,64 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>102683833.IB</t>
+          <t>132680099.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.1</v>
+        <v>20.0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>5.1</v>
+        <v>20.0</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+          <t>1.50 ~ 1.90</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>17.42</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26嘉秀发展MTN003</t>
+          <t>26南电GN007(科创债)</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.7867</t>
+          <t>1.6296</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市嘉秀发展投资控股集团有限公司</t>
+          <t>中国南方电网有限责任公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C 27.59</t>
+          <t>B- 40.65</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2372,7 +2406,7 @@
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
@@ -2381,40 +2415,40 @@
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>5.54</v>
+        <v>1.3</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>1.27</v>
+        <v>2.0</v>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额5.10亿元,拟用于偿还发行人有息债务本金[23嘉秀发展PPN003]</t>
+          <t>本期绿色科技创新债券发行规模20亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营以及充电站项目建设</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2425,7 +2459,7 @@
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
@@ -2435,7 +2469,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市嘉秀发展投资控股集团有限公司2026年度第四期中期票据</t>
+          <t>中国南方电网有限责任公司2026年度第八期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2445,14 +2479,10 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK10" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-22</t>
+        </is>
+      </c>
+      <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -2470,32 +2500,32 @@
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2528,7 +2558,7 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26南电GN008(科创债)</t>
+          <t>26环球天津SCP005</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2538,60 +2568,64 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>132680099.IB</t>
+          <t>012682360.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>0.47Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>20.0</v>
+        <v>5.0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+          <t>1.32 ~ 1.62</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>40.98</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26南电GN007(科创债)</t>
+          <t>26环球天津SCP003</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4.91Y</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.6296</t>
+          <t>1.6380</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司</t>
+          <t>通用环球国际融资租赁(天津)有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 40.65</t>
+          <t>C- 10.79</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2606,7 +2640,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -2614,20 +2648,16 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U11" s="4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V11" s="4" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.63%~1.67%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -2638,28 +2668,28 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模20亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营以及充电站项目建设</t>
+          <t>本期超短期融资券发行金额为5亿元,用于偿还发行人存量有息债务</t>
         </is>
       </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>渤海银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
@@ -2669,7 +2699,7 @@
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司2026年度第八期绿色科技创新债券</t>
+          <t>通用环球国际融资租赁(天津)有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
@@ -2679,7 +2709,7 @@
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
+          <t>2027-03-19</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
@@ -2700,32 +2730,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2753,12 +2783,14 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ11" s="3"/>
+      <c r="AZ11" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26环球天津SCP005</t>
+          <t>26京国资SCP001</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2768,60 +2800,64 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>012682360.IB</t>
+          <t>012682356.IB</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>0.47Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.62</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+          <t>1.30 ~ 1.50</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>15.72</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26环球天津SCP003</t>
+          <t>24国管01</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>330D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.6380</t>
+          <t>1.4873</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/1.5100</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>通用环球国际融资租赁(天津)有限公司</t>
+          <t>北京国有资本运营管理有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C- 10.79</t>
+          <t>B- 36.00</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2831,12 +2867,12 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
@@ -2848,12 +2884,12 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>1.63%~1.67%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
@@ -2861,20 +2897,24 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z12" s="3"/>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行金额为5亿元,用于偿还发行人存量有息债务</t>
+          <t>本期债务融资工具发行规模为人民币10亿元，发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司,中国邮政储蓄银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
         </is>
       </c>
       <c r="AD12" s="3"/>
@@ -2885,7 +2925,7 @@
       </c>
       <c r="AF12" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG12" s="3" t="inlineStr">
@@ -2895,7 +2935,7 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>通用环球国际融资租赁(天津)有限公司2026年度第五期超短期融资券</t>
+          <t>北京国有资本运营管理有限公司2026年度第一期超短期融资券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2905,7 +2945,7 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2027-03-19</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK12" s="3"/>
@@ -2926,32 +2966,32 @@
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR12" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2979,14 +3019,12 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ12" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ12" s="3"/>
     </row>
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26京国资SCP001</t>
+          <t>26衢产PPN001</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2994,62 +3032,56 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>012682356.IB</t>
-        </is>
-      </c>
+      <c r="C13" s="3"/>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>24国管01</t>
+          <t>26衢产02</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>330D</t>
+          <t>2.67Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.4873</t>
+          <t>1.7084</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.5100</t>
+          <t>--/1.7100</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司</t>
+          <t>衢州市产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 36.00</t>
+          <t>B- 38.75</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3059,29 +3091,31 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 10:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U13" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>4.54</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3089,30 +3123,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
+      <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-衢州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币10亿元，发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
+          <t>本期发行人发行的定向债务融资工具基础发行规模为0亿元,发行金额上限为5亿元,募集资金拟全部用于偿还公司银行贷款。[23衢州控股PPN001]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,平安银行股份有限公司</t>
+          <t>长江证券股份有限公司,国泰海通证券股份有限公司,杭州银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,恒丰银行股份有限公司,财通证券股份有限公司,上海银行股份有限公司,中信银行股份有限公司,宁波银行股份有限公司,中国建设银行股份有限公司,上海浦东发展银行股份有限公司,浙商银行股份有限公司,南京银行股份有限公司,徽商银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
@@ -3127,35 +3157,39 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司2026年度第一期超短期融资券</t>
+          <t>衢州市产业投资控股集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>产业</t>
@@ -3163,7 +3197,7 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
@@ -3216,7 +3250,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26衢产PPN001</t>
+          <t>26润业投资PPN002B</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3227,53 +3261,57 @@
       <c r="C14" s="3"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>5.0</v>
+        <v>2.5</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>64.42</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26衢产02</t>
+          <t>26润业01</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>2.67Y</t>
+          <t>2.52Y+2.00Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.7084</t>
+          <t>1.8450</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.7100</t>
+          <t>1.8900/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>衢州市产业投资控股集团有限公司</t>
+          <t>河源市润业投资有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 38.75</t>
+          <t>C- 15.95</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3283,52 +3321,52 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-24 10:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>4.54</v>
+        <v>3.05</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>浙江省-衢州市</t>
+          <t>广东省-河源市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期发行人发行的定向债务融资工具基础发行规模为0亿元,发行金额上限为5亿元,募集资金拟全部用于偿还公司银行贷款。[23衢州控股PPN001]</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>长江证券股份有限公司,国泰海通证券股份有限公司,杭州银行股份有限公司,中国邮政储蓄银行股份有限公司,中信建投证券股份有限公司,恒丰银行股份有限公司,财通证券股份有限公司,上海银行股份有限公司,中信银行股份有限公司,宁波银行股份有限公司,中国建设银行股份有限公司,上海浦东发展银行股份有限公司,浙商银行股份有限公司,南京银行股份有限公司,徽商银行股份有限公司,华夏银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
@@ -3349,7 +3387,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>衢州市产业投资控股集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种二)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3359,17 +3397,17 @@
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK14" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
@@ -3379,37 +3417,37 @@
       </c>
       <c r="AN14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>8.5*无效</t>
         </is>
       </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3442,7 +3480,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26润业投资PPN002B</t>
+          <t>26海螺集团MTN002(科创债/并购)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3450,56 +3488,66 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>102683838.IB</t>
+        </is>
+      </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F15" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>17.42</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26润业01</t>
+          <t>26海螺集团MTN001(科创债)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2.52Y+2.00Y</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.8450</t>
+          <t>1.7555</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.8900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司</t>
+          <t>安徽海螺集团有限责任公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 15.95</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3509,12 +3557,12 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3523,44 +3571,46 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V15" s="3"/>
+        <v>4.5</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>1.28</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>广东省-河源市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
+          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3575,12 +3625,12 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种二)</t>
+          <t>安徽海螺集团有限责任公司2026年度第二期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ15" s="3" t="inlineStr">
@@ -3610,32 +3660,32 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>8.5*无效</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3668,7 +3718,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN002(科创债/并购)</t>
+          <t>26夏商SCP028</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3678,55 +3728,59 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683838.IB</t>
+          <t>012682357.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.22Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+          <t>1.21 ~ 1.51</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>33.1</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN001(科创债)</t>
+          <t>26夏商SCP026</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>78D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.7555</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/1.4900</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -3746,7 +3800,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3754,47 +3808,43 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U16" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>1.28</v>
-      </c>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
+          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于用于补充发行人子公司厦门夏商民昇贸易有限公司营运资金。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国民生银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
@@ -3809,7 +3859,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司2026年度第二期科技创新债券(并购)</t>
+          <t>厦门夏商集团有限公司2026年度第二十八期超短期融资券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3819,12 +3869,12 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
+          <t>2026-12-19</t>
         </is>
       </c>
       <c r="AK16" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL16" s="3" t="inlineStr">
@@ -3849,27 +3899,27 @@
       </c>
       <c r="AP16" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3897,75 +3947,75 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP028</t>
+          <t>26宁德时代MTN008B(科创债)(取消发行)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 18:30</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>012682357.IB</t>
+          <t>DY102683832.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0.22Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>25.0</v>
+      </c>
+      <c r="F17" s="3"/>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.21 ~ 1.51</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP026</t>
+          <t>26宁德时代MTN007B(科创债)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>78D</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.7410</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.4900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>宁德时代新能源科技股份有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>B- 38.15</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3992,44 +4042,44 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>福建省-宁德市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元，扣除承销费后全部用于用于补充发行人子公司厦门夏商民昇贸易有限公司营运资金。</t>
+          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4039,7 +4089,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十八期超短期融资券</t>
+          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4049,12 +4099,12 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2026-12-19</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK17" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL17" s="3" t="inlineStr">
@@ -4064,7 +4114,7 @@
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4079,27 +4129,27 @@
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>电源设备</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4127,14 +4177,12 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ17" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ17" s="3"/>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN008B(科创债)</t>
+          <t>26宁德时代MTN008(科创债)</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4144,50 +4192,54 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683832.IB</t>
+          <t>102683831.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
         <v>25.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>25.0</v>
+        <v>50.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+          <t>1.40 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>8.42</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN007B(科创债)</t>
+          <t>26宁德时代MTN007A(科创债)</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>2.99Y+2.00Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.7410</t>
+          <t>1.6700</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
@@ -4220,7 +4272,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>1.428</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -4229,7 +4283,7 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.69%~1.79%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4271,7 +4325,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种二)</t>
+          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4336,7 +4390,7 @@
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4346,7 +4400,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4364,70 +4418,72 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN008A(科创债)</t>
+          <t>26柯桥03</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:30</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683831.IB</t>
+          <t>284145.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5+2</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>25.0</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>25.0</v>
-      </c>
+        <v>20.0</v>
+      </c>
+      <c r="F19" s="3"/>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>43.88</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN007A(科创债)</t>
+          <t>26绍兴柯桥PPN001</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.99Y+2.00Y</t>
+          <t>4.44Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.6700</t>
+          <t>1.9325</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.6700/--</t>
+          <t>1.9700/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司</t>
+          <t>绍兴市柯桥区建设集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 38.15</t>
+          <t>C 28.59</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4437,7 +4493,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4450,125 +4506,119 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U19" s="4" t="n">
-        <v>1.43</v>
-      </c>
+      <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>福建省-宁德市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23柯桥01]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券(品种一)</t>
+          <t>绍兴市柯桥区建设集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
+          <t>2033-09-28</t>
+        </is>
+      </c>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
           <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK19" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>电力设备制造</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>其他电力设备</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>其他电力设备</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>电源设备</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV19" s="3" t="inlineStr">
@@ -4596,7 +4646,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26柯桥03</t>
+          <t>26方大01</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4606,62 +4656,62 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>284145.SH</t>
+          <t>284123.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5+2</t>
+          <t>2+1</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>20.0</v>
+        <v>10.0</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>4.30 ~ 6.30</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.94</v>
+        <v>5.5</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>43.88</v>
+        <v>421.07</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26绍兴柯桥PPN001</t>
+          <t>24辽宁方大MTN001</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>4.44Y</t>
+          <t>218D</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.9325</t>
+          <t>5.9380</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.9700/--</t>
+          <t>--/5.5000</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区建设集团有限公司</t>
+          <t>辽宁方大集团实业有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C 28.59</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4681,21 +4731,17 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X20" s="3" t="inlineStr">
-        <is>
-          <t>1.83%~1.93%</t>
-        </is>
-      </c>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X20" s="3"/>
       <c r="Y20" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -4704,17 +4750,17 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金[23柯桥01]</t>
+          <t>本期债券发行规模为不超过人民币10.00亿元(含10.00亿元),债券募集资金扣除发行费用后,拟全部用于偿还到期的有息债务。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,中信建投证券股份有限公司,国投证券股份有限公司</t>
+          <t>中国银河证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4725,7 +4771,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4735,7 +4781,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区建设集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>辽宁方大集团实业有限公司2026年面向专业投资者非公开发行公司债券(高成长产业债)(第一期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4745,10 +4791,14 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2033-09-28</t>
-        </is>
-      </c>
-      <c r="AK20" s="3"/>
+          <t>2029-09-29</t>
+        </is>
+      </c>
+      <c r="AK20" s="3" t="inlineStr">
+        <is>
+          <t>休9</t>
+        </is>
+      </c>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t/>
@@ -4756,47 +4806,47 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
+          <t>2028-09-29</t>
         </is>
       </c>
       <c r="AV20" s="3" t="inlineStr">
@@ -4824,7 +4874,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26方大01</t>
+          <t>26港兴02</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4834,64 +4884,52 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>284123.SH</t>
+          <t>283964.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2+1</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>4.30 ~ 6.30</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.5</v>
+        <v>2.12</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>421.07</v>
+        <v>71.42</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>24辽宁方大MTN001</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>218D</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>5.9380</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/5.5000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>辽宁方大集团实业有限公司</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="inlineStr">
-        <is>
-          <t>B 55.00</t>
-        </is>
-      </c>
+          <t>响水县港兴建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="P21" s="3"/>
       <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -4909,16 +4947,12 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
-      <c r="W21" s="3" t="inlineStr">
-        <is>
-          <t>7+</t>
-        </is>
-      </c>
+      <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3" t="inlineStr">
         <is>
@@ -4928,20 +4962,24 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过人民币10.00亿元(含10.00亿元),债券募集资金扣除发行费用后,拟全部用于偿还到期的有息债务。</t>
+          <t>本期债券募集资金扣除发行费用和受托管理费用后,拟全部用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3"/>
+          <t>开源证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>湖南财鑫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE21" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4949,7 +4987,7 @@
       </c>
       <c r="AF21" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG21" s="3" t="inlineStr">
@@ -4959,7 +4997,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>辽宁方大集团实业有限公司2026年面向专业投资者非公开发行公司债券(高成长产业债)(第一期)</t>
+          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4969,12 +5007,12 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK21" s="3" t="inlineStr">
         <is>
-          <t>休9</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL21" s="3" t="inlineStr">
@@ -4989,7 +5027,7 @@
       </c>
       <c r="AN21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO21" s="3" t="inlineStr">
@@ -4997,11 +5035,7 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+      <c r="AP21" s="3"/>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
           <t>综合</t>
@@ -5009,32 +5043,32 @@
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
         <is>
-          <t>2028-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX21" s="3" t="inlineStr">
@@ -5052,7 +5086,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26同舟02</t>
+          <t>26港兴01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5062,43 +5096,39 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>283937.SH</t>
+          <t>283963.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>3.5</v>
+        <v>4.0</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>61.42</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>25中核二二GN001(科创债)</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>2.24Y+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
@@ -5108,7 +5138,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司</t>
+          <t>响水县港兴建设发展有限公司</t>
         </is>
       </c>
       <c r="P22" s="3"/>
@@ -5129,43 +5159,39 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t>7+</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t>2.30%~2.40%</t>
-        </is>
-      </c>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用和受托管理费用后,拟全部用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC22" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD22" s="3"/>
+          <t>开源证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr">
+        <is>
+          <t>江苏省信用增进有限责任公司</t>
+        </is>
+      </c>
       <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5183,7 +5209,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5193,10 +5219,14 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
-        </is>
-      </c>
-      <c r="AK22" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK22" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL22" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5204,12 +5234,12 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO22" s="3" t="inlineStr">
@@ -5220,17 +5250,17 @@
       <c r="AP22" s="3"/>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
@@ -5240,17 +5270,17 @@
       </c>
       <c r="AU22" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW22" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX22" s="3" t="inlineStr">
@@ -5268,7 +5298,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26同舟01</t>
+          <t>26郑经K1</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5278,43 +5308,47 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>283936.SH</t>
+          <t>284034.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3+3+4</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.5</v>
+        <v>1.0</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>39.42</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25中核二二GN001(科创债)</t>
+          <t>26郑经01</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.24Y+2.00Y</t>
+          <t>2.31Y+2.00Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.6852</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5324,10 +5358,14 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P23" s="3"/>
+          <t>郑州经开资本集团有限公司</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>D+ 10.00</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -5335,7 +5373,7 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 16:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
@@ -5345,7 +5383,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U23" s="3"/>
@@ -5355,30 +5393,26 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>1.95%~2.05%</t>
-        </is>
-      </c>
+      <c r="X23" s="3"/>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不低于0.70亿元募集资金通过发行人本部或子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余资金用于偿还有息负债。</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
+          <t>申万宏源证券有限公司,东兴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
@@ -5399,7 +5433,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>郑州经开资本集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5409,10 +5443,14 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5420,33 +5458,37 @@
       </c>
       <c r="AM23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP23" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
@@ -5456,7 +5498,7 @@
       </c>
       <c r="AU23" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV23" s="3" t="inlineStr">
@@ -5484,7 +5526,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26港兴02</t>
+          <t>26澄港01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5494,7 +5536,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>283964.SH</t>
+          <t>525027.SZ</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -5503,66 +5545,84 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.0</v>
+        <v>8.0</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.30 ~ 2.30</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>71.42</v>
+        <v>40.42</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>24江阴临港MTN001</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>1.14Y</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>1.5659</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>江阴临港新城开发建设有限公司</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>C+ 32.94</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>09-24 16:00</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>响水县港兴建设发展有限公司</t>
-        </is>
-      </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t>09-24 15:00</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U24" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="n">
+        <v>2.44</v>
+      </c>
       <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>6+</t>
+        </is>
+      </c>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="inlineStr">
         <is>
@@ -5572,22 +5632,22 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用和受托管理费用后,拟全部用于偿还到期债务。</t>
+          <t>本期债券发行总额不超过8.00亿元,公司仅可将本期债券募集资金用于偿还到期公司债券本金[21澄港04]</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>开源证券股份有限公司</t>
+          <t>中信证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3" t="inlineStr">
         <is>
-          <t>湖南财鑫融资担保有限公司</t>
+          <t>中证信用融资担保有限公司</t>
         </is>
       </c>
       <c r="AE24" s="3" t="inlineStr">
@@ -5602,29 +5662,25 @@
       </c>
       <c r="AG24" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>江阴临港新城开发建设有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5632,38 +5688,42 @@
       </c>
       <c r="AM24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP24" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5696,17 +5756,17 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26港兴01</t>
+          <t>26安建02</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-24 19:00</t>
+          <t>09-24 18:30</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>283963.SH</t>
+          <t>284001.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5715,67 +5775,87 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>4.0</v>
+        <v>5.6</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>61.42</v>
+        <v>57.42</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>26安建01</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>4.75Y</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>1.9314</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>浙江安吉建设控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>D- 0.72</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>09-24 15:00</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>响水县港兴建设发展有限公司</t>
-        </is>
-      </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>09-24 15:00</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>7+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>1.93%~2.03%</t>
+        </is>
+      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -5784,24 +5864,20 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用和受托管理费用后,拟全部用于偿还到期债务。</t>
+          <t>本期公司债券计划募集资金为5.6亿元,扣除发行费用后,拟全部用于偿还发行人赎回的公司债券本金。[23安建02]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>开源证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD25" s="3" t="inlineStr">
-        <is>
-          <t>江苏省信用增进有限责任公司</t>
-        </is>
-      </c>
+          <t>财通证券股份有限公司,国金证券股份有限公司,浙商证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5819,7 +5895,7 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>浙江安吉建设控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
@@ -5829,14 +5905,10 @@
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK25" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
           <t/>
@@ -5849,33 +5921,37 @@
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP25" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -5885,7 +5961,7 @@
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW25" s="3" t="inlineStr">
@@ -5908,7 +5984,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26郑经K1</t>
+          <t>26惠鑫01</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -5918,47 +5994,47 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>284034.SH</t>
+          <t>284108.SH</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.0</v>
+        <v>7.57</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.8</v>
+        <v>2.0</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>39.42</v>
+        <v>59.42</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26郑经01</t>
+          <t>25惠鑫01</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>2.31Y+2.00Y</t>
+          <t>3.66Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.6852</t>
+          <t>1.8229</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -5968,12 +6044,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>郑州经开资本集团有限公司</t>
+          <t>无锡惠鑫汇资产经营管理有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>D+ 10.00</t>
+          <t>D- 0.72</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -5983,7 +6059,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>09-24 16:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -5993,7 +6069,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U26" s="3"/>
@@ -6003,26 +6079,30 @@
           <t>7+</t>
         </is>
       </c>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1.83%~1.93%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不低于0.70亿元募集资金通过发行人本部或子公司对投资于科技创新类企业的基金出资或用于置换一年以内投资于科技创新企业的基金出资,剩余资金用于偿还有息负债。</t>
+          <t>本期债券拟将募集资金7.57亿元用于偿还到期公司债券本金[24惠鑫01,23惠鑫04]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>申万宏源证券有限公司,东兴证券股份有限公司</t>
+          <t>东吴证券股份有限公司,天风证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
@@ -6043,7 +6123,7 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>郑州经开资本集团有限公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)</t>
+          <t>无锡惠鑫汇资产经营管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
@@ -6053,14 +6133,10 @@
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK26" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-29</t>
+        </is>
+      </c>
+      <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6068,22 +6144,22 @@
       </c>
       <c r="AM26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6093,22 +6169,22 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV26" s="3" t="inlineStr">
@@ -6118,7 +6194,7 @@
       </c>
       <c r="AW26" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX26" s="3" t="inlineStr">
@@ -6136,57 +6212,57 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26澄港01</t>
+          <t>26柯资03</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-24 19:00</t>
+          <t>09-24 18:30</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>525027.SZ</t>
+          <t>284115.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>40.42</v>
+        <v>41.07</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24江阴临港MTN001</t>
+          <t>26柯资02</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>1.14Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.5659</t>
+          <t>1.6910</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6196,12 +6272,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>江阴临港新城开发建设有限公司</t>
+          <t>绍兴市柯桥区国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.94</t>
+          <t>C+ 30.27</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6211,7 +6287,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-24 16:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6221,17 +6297,21 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X27" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6240,24 +6320,20 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行总额不超过8.00亿元,公司仅可将本期债券募集资金用于偿还到期公司债券本金[21澄港04]</t>
+          <t>本期债券发行规模为不超过10亿元(含10亿元),募集资金拟全部用于偿还到期公司债券的本金。[23柯资05,23柯资06]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD27" s="3" t="inlineStr">
-        <is>
-          <t>中证信用融资担保有限公司</t>
-        </is>
-      </c>
+          <t>国信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD27" s="3"/>
       <c r="AE27" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -6270,22 +6346,22 @@
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>江阴临港新城开发建设有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>绍兴市柯桥区国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6301,32 +6377,32 @@
       </c>
       <c r="AN27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
@@ -6341,7 +6417,7 @@
       </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW27" s="3" t="inlineStr">
@@ -6364,17 +6440,17 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26安建02</t>
+          <t>26句容03</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:30</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>284001.SH</t>
+          <t>283950.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -6383,53 +6459,53 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>5.6</v>
+        <v>9.0</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.98</v>
+        <v>2.0</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>57.42</v>
+        <v>59.42</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26安建01</t>
+          <t>26句容01</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>4.72Y</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.9314</t>
+          <t>1.9886</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1000/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>浙江安吉建设控股集团有限公司</t>
+          <t>江苏句容福地生态科技有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>D- 0.72</t>
+          <t>B- 35.73</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6449,19 +6525,19 @@
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.93%~2.03%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6472,17 +6548,17 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>江苏省-镇江市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券计划募集资金为5.6亿元,扣除发行费用后,拟全部用于偿还发行人赎回的公司债券本金。[23安建02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将9.00亿元用于偿还回售的公司债券本金[23句容04]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司,国金证券股份有限公司,浙商证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
@@ -6503,7 +6579,7 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>浙江安吉建设控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏句容福地生态科技有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
@@ -6513,10 +6589,14 @@
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
-      <c r="AK28" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK28" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t/>
@@ -6524,37 +6604,37 @@
       </c>
       <c r="AM28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
@@ -6592,57 +6672,55 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26惠鑫01</t>
+          <t>26浙商证券CP006</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>09-24 19:00</t>
+          <t>09-24 17:00</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>284108.SH</t>
+          <t>072610196.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.66Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.57</v>
-      </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
+        <v>15.0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="G29" s="3"/>
       <c r="H29" s="4" t="n">
-        <v>2.0</v>
+        <v>1.52</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>59.42</v>
+        <v>30.72</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>25惠鑫01</t>
+          <t>26浙商证券CP005</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>3.66Y</t>
+          <t>274D</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.8229</t>
+          <t>1.5251</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6652,12 +6730,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>无锡惠鑫汇资产经营管理有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>D- 0.72</t>
+          <t>B- 35.25</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6667,7 +6745,7 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
@@ -6677,46 +6755,42 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
-        </is>
-      </c>
-      <c r="AB29" s="3" t="inlineStr">
-        <is>
-          <t>本期债券拟将募集资金7.57亿元用于偿还到期公司债券本金[24惠鑫01,23惠鑫04]</t>
-        </is>
-      </c>
+          <t>浙江省-杭州市</t>
+        </is>
+      </c>
+      <c r="AB29" s="3"/>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,天风证券股份有限公司</t>
+          <t>浙商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
@@ -6726,68 +6800,68 @@
       </c>
       <c r="AG29" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>无锡惠鑫汇资产经营管理有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>浙商证券股份有限公司2026年度第六期短期融资券</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2031-09-29</t>
+          <t>2027-05-26</t>
         </is>
       </c>
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6820,72 +6894,70 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26柯资03</t>
+          <t>26国泰海通CP010</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:30</t>
+          <t>09-24 17:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>284115.SH</t>
+          <t>072610197.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.91Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
+        <v>40.0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G30" s="3"/>
       <c r="H30" s="4" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>41.07</v>
+        <v>28.99</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>26柯资02</t>
+          <t>26国泰海通CP006</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.78Y</t>
+          <t>264D</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1.6910</t>
+          <t>1.4951</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区国有资产投资经营集团有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.27</t>
+          <t>A- 68.21</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -6895,7 +6967,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -6912,39 +6984,35 @@
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.48%~1.52%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
-        </is>
-      </c>
-      <c r="AB30" s="3" t="inlineStr">
-        <is>
-          <t>本期债券发行规模为不超过10亿元(含10亿元),募集资金拟全部用于偿还到期公司债券的本金。[23柯资05,23柯资06]</t>
-        </is>
-      </c>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB30" s="3"/>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -6954,33 +7022,33 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>国泰海通证券股份有限公司2026年度第十期短期融资券</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2027-08-26</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN30" s="3" t="inlineStr">
@@ -6990,32 +7058,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7048,72 +7116,74 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26句容03</t>
+          <t>26中交三航SCP023</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>09-24 19:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283950.SH</t>
+          <t>012682353.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="F31" s="3"/>
+        <v>5.0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.0</v>
+        <v>1.35</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>59.42</v>
+        <v>16.4</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26句容01</t>
+          <t>26中交三航SCP019</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.72Y</t>
+          <t>97D</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.9886</t>
+          <t>1.5002</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>2.1000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>江苏句容福地生态科技有限公司</t>
+          <t>中交第三航务工程局有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>B- 35.73</t>
+          <t>C+ 30.74</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7123,12 +7193,12 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -7136,125 +7206,125 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
+      <c r="U31" s="4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-镇江市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将9.00亿元用于偿还回售的公司债券本金[23句容04]</t>
+          <t>本期发行金额为5亿元，全部用于归还发行人本部有息负债</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国金证券股份有限公司</t>
+          <t>广发银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG31" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>江苏句容福地生态科技有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>中交第三航务工程局有限公司2026年度第二十三期超短期融资券</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK31" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="AK31" s="3"/>
       <c r="AL31" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AQ31" s="3" t="inlineStr">
+        <is>
+          <t>建筑施工</t>
+        </is>
+      </c>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>专业工程</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>市政路桥</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO31" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP31" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ31" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR31" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV31" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -7275,107 +7345,115 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ31" s="3"/>
+      <c r="AZ31" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26浙商证券CP006</t>
+          <t>26东航股MTN001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>072610196.IB</t>
+          <t>102683837.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>0.66Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G32" s="3"/>
+        <v>16.0</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>1.20 ~ 1.80</t>
+        </is>
+      </c>
       <c r="H32" s="4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>30.72</v>
+        <v>24.07</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>25东航股MTN006</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2.21Y</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>1.6011</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>1.6200/--</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>中国东方航空股份有限公司</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>B+ 57.72</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>09-24 09:00</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>26浙商证券CP005</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>274D</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>1.5251</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>浙商证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t>B- 35.25</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>09-24 09:00</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
       <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
+      <c r="V32" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
@@ -7386,24 +7464,28 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
-        </is>
-      </c>
-      <c r="AB32" s="3"/>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行金额为16亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金。</t>
+        </is>
+      </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG32" s="3" t="inlineStr">
@@ -7413,7 +7495,7 @@
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司2026年度第六期短期融资券</t>
+          <t>中国东方航空股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
@@ -7423,7 +7505,7 @@
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2027-05-26</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
@@ -7434,7 +7516,7 @@
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
@@ -7444,32 +7526,32 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR32" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS32" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT32" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU32" s="3" t="inlineStr">
@@ -7502,70 +7584,74 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP010</t>
+          <t>26海螺集团MTN003(科创债/并购)</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>072610197.IB</t>
+          <t>102683836.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.91Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>40.0</v>
+        <v>10.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="G33" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.10</t>
+        </is>
+      </c>
       <c r="H33" s="4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>28.99</v>
+        <v>17.42</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP006</t>
+          <t>26海螺集团MTN001(科创债)</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>264D</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.4951</t>
+          <t>1.7555</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.5200/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>安徽海螺集团有限责任公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>A- 68.21</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7580,7 +7666,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -7588,16 +7674,20 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
+      <c r="U33" s="4" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.48%~1.52%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7608,19 +7698,23 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB33" s="3"/>
+          <t>安徽省-芜湖市</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
+        </is>
+      </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7635,7 +7729,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第十期短期融资券</t>
+          <t>安徽海螺集团有限责任公司2026年度第三期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7645,10 +7739,14 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2027-08-26</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -7656,7 +7754,7 @@
       </c>
       <c r="AM33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN33" s="3" t="inlineStr">
@@ -7666,32 +7764,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7724,7 +7822,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26中交三航SCP023</t>
+          <t>26乌江水电GN005</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7734,60 +7832,64 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>012682353.IB</t>
+          <t>132680100.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+          <t>1.40 ~ 1.65</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>31.72</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26中交三航SCP019</t>
+          <t>26乌江水电GN002</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>97D</t>
+          <t>179D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.5002</t>
+          <t>1.5294</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>中交第三航务工程局有限公司</t>
+          <t>贵州乌江水电开发有限责任公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.74</t>
+          <t>C+ 30.84</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7802,7 +7904,7 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -7811,19 +7913,19 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.54</v>
+        <v>3.07</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.0</v>
+        <v>6.5</v>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7834,17 +7936,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为5亿元，全部用于归还发行人本部有息负债</t>
+          <t>本期绿色超短期融资券发行金额3亿元,募集资金将全部用于偿还构皮滩水电站等6个水电站有息负债本金</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -7865,7 +7967,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>中交第三航务工程局有限公司2026年度第二十三期超短期融资券</t>
+          <t>贵州乌江水电开发有限责任公司2026年度第五期绿色超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7875,7 +7977,7 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
@@ -7901,27 +8003,27 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -7950,13 +8052,13 @@
         </is>
       </c>
       <c r="AZ34" s="4" t="n">
-        <v>0.0</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN001</t>
+          <t>26夏商SCP027</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7966,60 +8068,60 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102683837.IB</t>
+          <t>012682361.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>16.0</v>
+        <v>5.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>16.0</v>
+        <v>5.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.80</t>
+          <t>1.40 ~ 1.51</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>26夏商SCP026</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.21Y</t>
+          <t>78D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.6011</t>
+          <t>1.5100</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>1.5200/1.4900</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>厦门夏商集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>B+ 57.72</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8034,7 +8136,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
@@ -8043,49 +8145,47 @@
         </is>
       </c>
       <c r="U35" s="3"/>
-      <c r="V35" s="4" t="n">
-        <v>8.0</v>
-      </c>
+      <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为16亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金。</t>
+          <t>发行人本期发行超短期融资券5亿元,扣除承销费后全部用于偿还发行人即将到期的债务融资工具。[26夏商SCP020]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
@@ -8095,7 +8195,7 @@
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第一期中期票据</t>
+          <t>厦门夏商集团有限公司2026年度第二十七期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8105,7 +8205,7 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
@@ -8131,27 +8231,27 @@
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>航空</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>航空运输</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8184,7 +8284,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN003(科创债/并购)</t>
+          <t>26京国资SCP002</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8194,12 +8294,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>102683836.IB</t>
+          <t>012682358.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -8210,44 +8310,48 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+          <t>1.30 ~ 1.50</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>15.72</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN001(科创债)</t>
+          <t>24国管01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>330D</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.7555</t>
+          <t>1.4873</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/1.5100</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司</t>
+          <t>北京国有资本运营管理有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>B- 36.00</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8257,12 +8361,12 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
@@ -8271,19 +8375,17 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="V36" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>1.2</v>
+      </c>
+      <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8291,26 +8393,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z36" s="3"/>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
+          <t>本期债务融资工具发行规模为人民币10亿元,发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
+          <t>华夏银行股份有限公司,北京农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8325,7 +8431,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司2026年度第三期科技创新债券(并购)</t>
+          <t>北京国有资本运营管理有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8335,14 +8441,10 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK36" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-25</t>
+        </is>
+      </c>
+      <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -8365,27 +8467,27 @@
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8418,7 +8520,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26乌江水电GN005</t>
+          <t>26湖交投MTN004</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8428,60 +8530,64 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>132680100.IB</t>
+          <t>102683835.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.65</t>
-        </is>
-      </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>19.42</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>26乌江水电GN002</t>
+          <t>26湖交投MTN003</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>179D</t>
+          <t>2.98Y+2.00Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.5294</t>
+          <t>1.6831</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>1.7000/1.6400</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江水电开发有限责任公司</t>
+          <t>湖州市交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.84</t>
+          <t>B- 37.26</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8491,12 +8597,12 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
@@ -8505,19 +8611,17 @@
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>6.5</v>
-      </c>
+        <v>5.8</v>
+      </c>
+      <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.60%~1.70%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8528,28 +8632,28 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期绿色超短期融资券发行金额3亿元,募集资金将全部用于偿还构皮滩水电站等6个水电站有息负债本金</t>
+          <t>发行人本期中期票据基础发行规模为0亿元,发行金额上限为5.00亿元,拟全部用于偿还发行人债务融资工具本金[23湖交投MTN004]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,招商银行股份有限公司</t>
+          <t>东方证券股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8559,7 +8663,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江水电开发有限责任公司2026年度第五期绿色超短期融资券</t>
+          <t>湖州市交通投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8569,10 +8673,14 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK37" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK37" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL37" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -8590,37 +8698,37 @@
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>高速</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>高速公路</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8630,7 +8738,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8643,14 +8751,12 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ37" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ37" s="3"/>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP027</t>
+          <t>26靖江滨江PPN002</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8658,62 +8764,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>012682361.IB</t>
-        </is>
-      </c>
+      <c r="C38" s="3"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.51</t>
-        </is>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+          <t>1.38 ~ 2.10</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>40.91</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP026</t>
+          <t>25靖滨03</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>78D</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.6568</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.4900</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>C 25.71</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8728,7 +8832,7 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -8736,43 +8840,47 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
+      <c r="U38" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元,扣除承销费后全部用于偿还发行人即将到期的债务融资工具。[26夏商SCP020]</t>
+          <t>本期定向债务融资工具发行金额2.5亿元,用于置换有息债务[26靖江滨江SCP001]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8787,17 +8895,17 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十七期超短期融资券</t>
+          <t>靖江市滨江新城投资开发有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2028-09-28</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
@@ -8818,32 +8926,32 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8876,7 +8984,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26京国资SCP002</t>
+          <t>26润业投资PPN002A</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -8884,62 +8992,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>012682358.IB</t>
-        </is>
-      </c>
+      <c r="C39" s="3"/>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
-        </is>
-      </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>46.42</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>24国管01</t>
+          <t>26润业01</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>330D</t>
+          <t>2.52Y+2.00Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.4873</t>
+          <t>1.8450</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.5100</t>
+          <t>1.8900/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司</t>
+          <t>河源市润业投资有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 36.00</t>
+          <t>C- 15.95</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8949,12 +9055,12 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -8963,48 +9069,44 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>1.2</v>
+        <v>2.97</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z39" s="3" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-河源市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币10亿元,发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司,北京农村商业银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9019,20 +9121,24 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司2026年度第二期超短期融资券</t>
+          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK39" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL39" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -9050,37 +9156,37 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8.5*无效</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV39" s="3" t="inlineStr">
@@ -9090,7 +9196,7 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -9108,7 +9214,7 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26湖交投MTN004</t>
+          <t>26东阳国资PPN002</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -9116,62 +9222,60 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>102683835.IB</t>
-        </is>
-      </c>
+      <c r="C40" s="3"/>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F40" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>44.42</v>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26湖交投MTN003</t>
+          <t>26东阳国资PPN001A</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>2.98Y+2.00Y</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.6831</t>
+          <t>1.8376</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>1.7000/1.6400</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>湖州市交通投资集团有限公司</t>
+          <t>东阳市国有资产投资有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>B- 37.26</t>
+          <t>C- 17.96</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9181,12 +9285,12 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
@@ -9195,44 +9299,46 @@
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="V40" s="3"/>
+        <v>4.4</v>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.60%~1.70%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模为0亿元,发行金额上限为5.00亿元,拟全部用于偿还发行人债务融资工具本金[23湖交投MTN004]</t>
+          <t>发行人本期拟发行规模为人民币5亿元，用于偿还有息负债[23东阳国资PPN003]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,招商银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9247,12 +9353,12 @@
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>湖州市交通投资集团有限公司2026年度第四期中期票据</t>
+          <t>东阳市国有资产投资有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
@@ -9282,37 +9388,37 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>高速</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>高速公路</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV40" s="3" t="inlineStr">
@@ -9322,7 +9428,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9340,7 +9446,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26靖江滨江PPN002</t>
+          <t>26特区建工MTN001</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9348,56 +9454,66 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C41" s="3"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>102683829.IB</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>8.0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.38 ~ 2.10</t>
-        </is>
-      </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>38.07</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>25靖滨03</t>
+          <t>24建工02</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>2.46Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.6568</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/1.6100</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>深圳市特区建工集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C 25.71</t>
+          <t>B- 42.38</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9412,7 +9528,7 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
@@ -9420,47 +9536,47 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U41" s="4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V41" s="4" t="n">
-        <v>2.0</v>
-      </c>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z41" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额2.5亿元,用于置换有息债务[26靖江滨江SCP001]</t>
+          <t>发行人本期中期票据募集资金8亿元,拟用于偿还银行借款</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9475,17 +9591,17 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年度第二期定向债务融资工具</t>
+          <t>深圳市特区建工集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2028-09-28</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9506,32 +9622,32 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
@@ -9564,64 +9680,70 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26润业投资PPN002A</t>
+          <t>26重庆银行债01</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
-        </is>
-      </c>
-      <c r="C42" s="3"/>
+          <t>09-24 17:00</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>212680058.IB</t>
+        </is>
+      </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+        <v>20.0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="G42" s="3"/>
+      <c r="H42" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>31.07</v>
+      </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>26润业01</t>
+          <t>26重庆银行小微债01(柜台)</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>2.52Y+2.00Y</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.8450</t>
+          <t>1.5952</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.8900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司</t>
+          <t>重庆银行股份有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>C- 15.95</t>
+          <t>A 71.85</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9631,12 +9753,12 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:30</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
@@ -9644,45 +9766,39 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U42" s="4" t="n">
-        <v>2.97</v>
-      </c>
+      <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>广东省-河源市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
-        </is>
-      </c>
-      <c r="AC42" s="3" t="inlineStr">
-        <is>
-          <t>中信建投证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展</t>
+        </is>
+      </c>
+      <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9697,32 +9813,28 @@
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种一)</t>
+          <t>重庆银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AN42" s="3" t="inlineStr">
@@ -9732,37 +9844,37 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>8.5*无效</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV42" s="3" t="inlineStr">
@@ -9772,7 +9884,7 @@
       </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
@@ -9790,7 +9902,7 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26东阳国资PPN002</t>
+          <t>26郑州交发MTN002(绿色)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -9798,56 +9910,66 @@
           <t>09-24 18:00</t>
         </is>
       </c>
-      <c r="C43" s="3"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>102683830.IB</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F43" s="3"/>
+      <c r="F43" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+          <t>1.40 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>41.07</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26东阳国资PPN001A</t>
+          <t>24郑州地铁GN002</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>1.12Y+N</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.8376</t>
+          <t>1.6185</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>东阳市国有资产投资有限公司</t>
+          <t>郑州交通发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 17.96</t>
+          <t>C- 16.21</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9862,7 +9984,7 @@
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
@@ -9870,43 +9992,47 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
+      <c r="U43" s="4" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>9.0</v>
+      </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行规模为人民币5亿元，用于偿还有息负债[23东阳国资PPN003]</t>
+          <t>本期发行金额上限10.00亿元,基础发行规模0亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司</t>
+          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -9921,24 +10047,20 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>东阳市国有资产投资有限公司2026年度第二期定向债务融资工具</t>
+          <t>郑州交通发展投资集团有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK43" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -9961,27 +10083,27 @@
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -9996,12 +10118,12 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY43" s="3" t="inlineStr">
@@ -10014,72 +10136,70 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26深圳特建MTN001</t>
+          <t>26同舟02</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>102683829.IB</t>
+          <t>283937.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>8.0</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+          <t>1.80 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>41.62</v>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>24建工02</t>
+          <t>25中核二二GN001(科创债)</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2.46Y</t>
+          <t>2.24Y+2.00Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.7875</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>深圳市特区建工集团有限公司</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t>B- 42.38</t>
-        </is>
-      </c>
+          <t>山东同舟产业控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P44" s="3"/>
       <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -10087,7 +10207,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10097,19 +10217,21 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U44" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="n">
+        <v>1.85</v>
+      </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.30%~2.40%</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -10117,30 +10239,26 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+      <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据募集资金8亿元,拟用于偿还银行借款</t>
+          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10150,50 +10268,46 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>深圳市特区建工集团有限公司2026年度第一期中期票据</t>
+          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2036-09-29</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="AP44" s="3"/>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
           <t>建筑施工</t>
@@ -10201,22 +10315,22 @@
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV44" s="3" t="inlineStr">
@@ -10226,7 +10340,7 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10244,55 +10358,57 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26重庆银行债01</t>
+          <t>26同舟01</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>212680058.IB</t>
+          <t>283936.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+3+4</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="G45" s="3"/>
+        <v>3.5</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>1.60 ~ 2.10</t>
+        </is>
+      </c>
       <c r="H45" s="4" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="I45" s="4" t="n">
-        <v>31.07</v>
+        <v>18.62</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>26重庆银行小微债01(柜台)</t>
+          <t>25中核二二GN001(科创债)</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>2.24Y+2.00Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>1.5952</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -10302,14 +10418,10 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="inlineStr">
-        <is>
-          <t>A 71.85</t>
-        </is>
-      </c>
+          <t>山东同舟产业控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P45" s="3"/>
       <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -10317,7 +10429,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:30</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10327,19 +10439,21 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="U45" s="3"/>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="n">
+        <v>1.87</v>
+      </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -10350,19 +10464,23 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展</t>
-        </is>
-      </c>
-      <c r="AC45" s="3"/>
+          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
@@ -10372,22 +10490,22 @@
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司2026年第一期金融债券</t>
+          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2036-09-29</t>
         </is>
       </c>
       <c r="AK45" s="3"/>
@@ -10398,47 +10516,43 @@
       </c>
       <c r="AM45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP45" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP45" s="3"/>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU45" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV45" s="3" t="inlineStr">
@@ -10448,7 +10562,7 @@
       </c>
       <c r="AW45" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX45" s="3" t="inlineStr">
@@ -10466,70 +10580,72 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26郑州交发MTN002(绿色)</t>
+          <t>26锡铁01</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>102683830.IB</t>
+          <t>284118.SH</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>5.0</v>
-      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+          <t>1.30 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>44.42</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>24郑州地铁GN002</t>
+          <t>26锡铁D1</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>1.12Y+N</t>
+          <t>315D</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.6185</t>
+          <t>1.5157</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司</t>
+          <t>无锡地铁集团有限公司</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>C- 16.21</t>
+          <t>C- 25.00</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10539,12 +10655,12 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
@@ -10553,11 +10669,9 @@
         </is>
       </c>
       <c r="U46" s="4" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="V46" s="4" t="n">
-        <v>9.0</v>
-      </c>
+        <v>5.16</v>
+      </c>
+      <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -10565,7 +10679,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -10576,23 +10690,23 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额上限10.00亿元,基础发行规模0亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
+          <t>本期债券募集资金拟全部用于置换自有资金偿还的公司债券本金[GY锡铁01]</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
+          <t>天风证券股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
@@ -10602,33 +10716,37 @@
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司2026年度第二期绿色中期票据</t>
+          <t>无锡地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
-        </is>
-      </c>
-      <c r="AK46" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK46" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="AN46" s="3" t="inlineStr">
@@ -10638,12 +10756,12 @@
       </c>
       <c r="AO46" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP46" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ46" s="3" t="inlineStr">
@@ -10663,7 +10781,7 @@
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>公交</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10678,12 +10796,12 @@
       </c>
       <c r="AW46" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX46" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY46" s="3" t="inlineStr">
@@ -10696,7 +10814,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26锡铁01</t>
+          <t>26皖国资MTN004(科创债)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10706,7 +10824,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>284118.SH</t>
+          <t>102683839.IB</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10715,38 +10833,40 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F47" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.30</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="I47" s="4" t="n">
-        <v>44.42</v>
+        <v>23.42</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>26锡铁D1</t>
+          <t>26皖国资MTN003</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>315D</t>
+          <t>2.87Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.5157</t>
+          <t>1.6623</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -10756,12 +10876,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>无锡地铁集团有限公司</t>
+          <t>安徽省国有资本运营控股集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>C- 25.00</t>
+          <t>B- 42.80</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10771,12 +10891,12 @@
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="T47" s="3" t="inlineStr">
@@ -10784,11 +10904,13 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U47" s="3"/>
+      <c r="U47" s="4" t="n">
+        <v>8.0667</v>
+      </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
@@ -10804,23 +10926,23 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金拟全部用于置换自有资金偿还的公司债券本金[GY锡铁01]</t>
+          <t>本期科技创新债券基础发行金额0亿元,本期发行金额上限6亿元,全部用于置换发行人一年内以股权投资形式对科技创新领域的资金投入。</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
       <c r="AE47" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF47" s="3" t="inlineStr">
@@ -10830,17 +10952,17 @@
       </c>
       <c r="AG47" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>无锡地铁集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>安徽省国有资本运营控股集团有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
@@ -10855,12 +10977,12 @@
       </c>
       <c r="AL47" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN47" s="3" t="inlineStr">
@@ -10875,27 +10997,27 @@
       </c>
       <c r="AP47" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ47" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-24.xlsx
+++ b/data/credit_bond_all_2026-09-24.xlsx
@@ -1250,7 +1250,9 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>1.42</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
@@ -3454,7 +3456,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26嘉秀发展MTN004</t>
+          <t>26海螺集团MTN002(科创债/并购)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3464,7 +3466,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683833.IB</t>
+          <t>102683838.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3473,21 +3475,21 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.1</v>
+        <v>10.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5.1</v>
+        <v>10.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>27.42</v>
+        <v>17.42</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -3496,17 +3498,17 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26嘉秀发展MTN003</t>
+          <t>26海螺集团MTN001(科创债)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.7867</t>
+          <t>1.7555</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -3516,12 +3518,12 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市嘉秀发展投资控股集团有限公司</t>
+          <t>安徽海螺集团有限责任公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 27.15</t>
+          <t>C+ 33.00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3536,7 +3538,7 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
@@ -3545,40 +3547,40 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>5.54</v>
+        <v>4.5</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.70%~1.80%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据发行金额5.10亿元,拟用于偿还发行人有息债务本金[23嘉秀发展PPN003]</t>
+          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,中国国际金融股份有限公司</t>
+          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD15" s="3"/>
@@ -3599,7 +3601,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>嘉兴市嘉秀发展投资控股集团有限公司2026年度第四期中期票据</t>
+          <t>安徽海螺集团有限责任公司2026年度第二期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3634,32 +3636,32 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3692,7 +3694,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26中广核租SCP006</t>
+          <t>26皖国资MTN004(科创债)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3702,64 +3704,64 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>012682355.IB</t>
+          <t>102683839.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>18.72</v>
+        <v>23.42</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26中广核租SCP004(绿色)</t>
+          <t>26皖国资MTN003</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>2.87Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.5380</t>
+          <t>1.6623</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6850/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>中广核国际融资租赁有限公司</t>
+          <t>安徽省国有资本运营控股集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C- 15.63</t>
+          <t>C+ 34.86</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3774,7 +3776,7 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
@@ -3782,48 +3784,50 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>8.0667</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.74%~1.84%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>安徽省</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金5亿元,拟用于偿还到期银行借款</t>
+          <t>本期科技创新债券基础发行金额0亿元,本期发行金额上限6亿元,全部用于置换发行人一年内以股权投资形式对科技创新领域的资金投入。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>上海银行股份有限公司,浙商银行股份有限公司</t>
+          <t>中信银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3833,7 +3837,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>中广核国际融资租赁有限公司2026年度第六期超短期融资券</t>
+          <t>安徽省国有资本运营控股集团有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3843,10 +3847,14 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK16" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -3864,7 +3872,7 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP16" s="3" t="inlineStr">
@@ -3874,22 +3882,22 @@
       </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3922,74 +3930,74 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN002(科创债/并购)</t>
+          <t>26宁德时代MTN008(科创债)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 18:30</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683838.IB</t>
+          <t>102683831.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.0</v>
+        <v>50.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>17.42</v>
+        <v>8.42</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN001(科创债)</t>
+          <t>26宁德时代MTN007A(科创债)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>2.99Y+2.00Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.7555</t>
+          <t>1.6700</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6700/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司</t>
+          <t>宁德时代新能源科技股份有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.00</t>
+          <t>B- 37.93</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4004,7 +4012,7 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
@@ -4013,19 +4021,17 @@
         </is>
       </c>
       <c r="U17" s="4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V17" s="4" t="n">
-        <v>1.28</v>
-      </c>
+        <v>1.428</v>
+      </c>
+      <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.61%~1.71%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4036,17 +4042,17 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>福建省-宁德市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
+          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -4057,7 +4063,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4067,7 +4073,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司2026年度第二期科技创新债券(并购)</t>
+          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4092,7 +4098,7 @@
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4112,27 +4118,27 @@
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>电源设备</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AV17" s="3" t="inlineStr">
@@ -4142,7 +4148,7 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
@@ -4160,7 +4166,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26皖国资MTN004(科创债)</t>
+          <t>26靖江滨江PPN002</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4170,64 +4176,64 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683839.IB</t>
+          <t>032690026.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.0</v>
+        <v>2.5</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>6.0</v>
+        <v>2.5</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.38 ~ 2.10</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>23.42</v>
+        <v>40.91</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26皖国资MTN003</t>
+          <t>25靖滨03</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.87Y</t>
+          <t>1.88Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.6623</t>
+          <t>1.6568</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.6850/--</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>安徽省国有资本运营控股集团有限公司</t>
+          <t>靖江市滨江新城投资开发有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.86</t>
+          <t>C 25.29</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4242,7 +4248,7 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
@@ -4251,44 +4257,46 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>8.0667</v>
-      </c>
-      <c r="V18" s="3"/>
+        <v>2.4</v>
+      </c>
+      <c r="V18" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.74%~1.84%</t>
+          <t>1.68%~1.78%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>安徽省</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债券基础发行金额0亿元,本期发行金额上限6亿元,全部用于置换发行人一年内以股权投资形式对科技创新领域的资金投入。</t>
+          <t>本期定向债务融资工具发行金额2.5亿元,用于置换有息债务[26靖江滨江SCP001]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4303,24 +4311,20 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>安徽省国有资本运营控股集团有限公司2026年度第四期科技创新债券</t>
+          <t>靖江市滨江新城投资开发有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-09-28</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -4343,27 +4347,27 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4396,74 +4400,70 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP027</t>
+          <t>26重庆银行债01</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 17:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>012682361.IB</t>
+          <t>212680058.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.18Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 1.51</t>
-        </is>
-      </c>
+        <v>20.0</v>
+      </c>
+      <c r="G19" s="3"/>
       <c r="H19" s="4" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>33.1</v>
+        <v>31.07</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26夏商SCP026</t>
+          <t>26重庆银行小微债01(柜台)</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>78D</t>
+          <t>2.88Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.5100</t>
+          <t>1.5952</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.4900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司</t>
+          <t>重庆银行股份有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B 51.36</t>
+          <t>A- 68.10</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 09:30</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4490,39 +4490,35 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>5+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>福建省-厦门市</t>
+          <t>重庆市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期发行超短期融资券5亿元,扣除承销费后全部用于偿还发行人即将到期的债务融资工具。[26夏商SCP020]</t>
-        </is>
-      </c>
-      <c r="AC19" s="3" t="inlineStr">
-        <is>
-          <t>招商银行股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展</t>
+        </is>
+      </c>
+      <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4537,7 +4533,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>厦门夏商集团有限公司2026年度第二十七期超短期融资券</t>
+          <t>重庆银行股份有限公司2026年第一期金融债券</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4547,7 +4543,7 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2026-12-04</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
@@ -4558,7 +4554,7 @@
       </c>
       <c r="AM19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="AN19" s="3" t="inlineStr">
@@ -4568,32 +4564,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4626,74 +4622,74 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN008(科创债)</t>
+          <t>26东航股MTN001</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:30</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>102683831.IB</t>
+          <t>102683837.IB</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>25.0</v>
+        <v>16.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>50.0</v>
+        <v>16.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.20 ~ 1.80</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8.42</v>
+        <v>24.07</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26宁德时代MTN007A(科创债)</t>
+          <t>25东航股MTN006</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.99Y+2.00Y</t>
+          <t>2.21Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.6700</t>
+          <t>1.6011</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.6700/--</t>
+          <t>1.6200/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司</t>
+          <t>中国东方航空股份有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 37.93</t>
+          <t>B 52.59</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4708,7 +4704,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
@@ -4716,18 +4712,18 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U20" s="4" t="n">
-        <v>1.428</v>
-      </c>
-      <c r="V20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.61%~1.71%</t>
+          <t>1.59%~1.69%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
@@ -4738,17 +4734,17 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>福建省-宁德市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模上限为50亿元，本期绿色科技创新债券募集资金拟全部用于发行人及下属锂离子电池生产项目的日常运营，包括原材料购置、设备维护和更新等，以及偿付因采购项目原材料等开具的银行承兑汇票、商业承兑汇票及融单等</t>
+          <t>本期中期票据发行金额为16亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金。</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4759,7 +4755,7 @@
       </c>
       <c r="AF20" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG20" s="3" t="inlineStr">
@@ -4769,7 +4765,7 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>宁德时代新能源科技股份有限公司2026年度第八期绿色科技创新债券</t>
+          <t>中国东方航空股份有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
@@ -4779,14 +4775,10 @@
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -4794,7 +4786,7 @@
       </c>
       <c r="AM20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN20" s="3" t="inlineStr">
@@ -4809,32 +4801,32 @@
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>航空</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>电源设备</t>
+          <t>航空运输</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV20" s="3" t="inlineStr">
@@ -4844,7 +4836,7 @@
       </c>
       <c r="AW20" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX20" s="3" t="inlineStr">
@@ -4862,7 +4854,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26靖江滨江PPN002</t>
+          <t>26特区建工MTN001</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4872,64 +4864,64 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>032690026.IB</t>
+          <t>102683829.IB</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>2Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.5</v>
+        <v>8.0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.5</v>
+        <v>8.0</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.38 ~ 2.10</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>40.91</v>
+        <v>38.07</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>25靖滨03</t>
+          <t>24建工02</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>1.88Y</t>
+          <t>2.46Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.6568</t>
+          <t>1.7875</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>--/1.6100</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司</t>
+          <t>深圳市特区建工集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C 25.29</t>
+          <t>C+ 30.69</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4944,7 +4936,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
@@ -4953,46 +4945,48 @@
         </is>
       </c>
       <c r="U21" s="4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>3.54</v>
+      </c>
+      <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.68%~1.78%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z21" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额2.5亿元,用于置换有息债务[26靖江滨江SCP001]</t>
+          <t>发行人本期中期票据募集资金8亿元,拟用于偿还银行借款</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF21" s="3" t="inlineStr">
@@ -5007,17 +5001,17 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>靖江市滨江新城投资开发有限公司2026年度第二期定向债务融资工具</t>
+          <t>深圳市特区建工集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2028-09-28</t>
+          <t>2029-09-28</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
@@ -5038,32 +5032,32 @@
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr">
@@ -5096,22 +5090,22 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26重庆银行债01</t>
+          <t>26南电GN008(科创债)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>09-24 17:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>212680058.IB</t>
+          <t>132680099.IB</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -5120,12 +5114,16 @@
       <c r="F22" s="4" t="n">
         <v>20.0</v>
       </c>
-      <c r="G22" s="3"/>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 1.90</t>
+        </is>
+      </c>
       <c r="H22" s="4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>31.07</v>
+        <v>17.42</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -5134,32 +5132,32 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>26重庆银行小微债01(柜台)</t>
+          <t>26南电GN007(科创债)</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2.88Y</t>
+          <t>4.91Y</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>1.5952</t>
+          <t>1.6296</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司</t>
+          <t>中国南方电网有限责任公司</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>A- 68.10</t>
+          <t>B- 40.49</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
@@ -5169,12 +5167,12 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:30</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
@@ -5182,16 +5180,20 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5202,24 +5204,28 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3" t="inlineStr">
         <is>
-          <t>重庆市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB22" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金将依据适用法律和监管部门的批准，用于满足发行人资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展</t>
-        </is>
-      </c>
-      <c r="AC22" s="3"/>
+          <t>本期绿色科技创新债券发行规模20亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营以及充电站项目建设</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF22" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG22" s="3" t="inlineStr">
@@ -5229,7 +5235,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>重庆银行股份有限公司2026年第一期金融债券</t>
+          <t>中国南方电网有限责任公司2026年度第八期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5239,7 +5245,7 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2031-09-22</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
@@ -5250,7 +5256,7 @@
       </c>
       <c r="AM22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AN22" s="3" t="inlineStr">
@@ -5260,32 +5266,32 @@
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP22" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ22" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr">
@@ -5318,7 +5324,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26东航股MTN001</t>
+          <t>26润业投资PPN002A</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5328,64 +5334,64 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>102683837.IB</t>
+          <t>032680544.IB</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>16.0</v>
+        <v>2.5</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>16.0</v>
+        <v>3.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.80</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>24.07</v>
+        <v>46.42</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>25东航股MTN006</t>
+          <t>26润业01</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>2.21Y</t>
+          <t>2.52Y+2.00Y</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>1.6011</t>
+          <t>1.8450</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>1.6200/--</t>
+          <t>1.8900/--</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司</t>
+          <t>河源市润业投资有限公司</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>B 52.59</t>
+          <t>C- 12.29</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -5395,12 +5401,12 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
@@ -5408,50 +5414,50 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="U23" s="3"/>
-      <c r="V23" s="4" t="n">
-        <v>8.0</v>
-      </c>
+      <c r="U23" s="4" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>1.59%~1.69%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-河源市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额为16亿元，拟用于公司本部及子公司归还付息性债务或补充营运资金。</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,上海浦东发展银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF23" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG23" s="3" t="inlineStr">
@@ -5461,70 +5467,74 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>中国东方航空股份有限公司2026年度第一期中期票据</t>
+          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种一)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>8.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
           <t>2029-09-28</t>
         </is>
       </c>
-      <c r="AK23" s="3"/>
-      <c r="AL23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AM23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO23" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ23" s="3" t="inlineStr">
-        <is>
-          <t>交通运输</t>
-        </is>
-      </c>
-      <c r="AR23" s="3" t="inlineStr">
-        <is>
-          <t>航空</t>
-        </is>
-      </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>航空</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>航空运输</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -5532,7 +5542,7 @@
       </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX23" s="3" t="inlineStr">
@@ -5550,7 +5560,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN003(科创债/并购)</t>
+          <t>26中交三航SCP023</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5560,49 +5570,49 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>102683836.IB</t>
+          <t>012682353.IB</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.25Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>17.42</v>
+        <v>16.4</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>26海螺集团MTN001(科创债)</t>
+          <t>26中交三航SCP019</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>4.46Y</t>
+          <t>97D</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.7555</t>
+          <t>1.5002</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -5612,12 +5622,12 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司</t>
+          <t>中交第三航务工程局有限公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.00</t>
+          <t>C 27.52</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5632,7 +5642,7 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
@@ -5641,19 +5651,19 @@
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>4.52</v>
+        <v>1.54</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -5664,28 +5674,28 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3" t="inlineStr">
         <is>
-          <t>安徽省-芜湖市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
+          <t>本期发行金额为5亿元，全部用于归还发行人本部有息负债</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
+          <t>广发银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
       <c r="AE24" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5695,7 +5705,7 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>安徽海螺集团有限责任公司2026年度第三期科技创新债券(并购)</t>
+          <t>中交第三航务工程局有限公司2026年度第二十三期超短期融资券</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
@@ -5705,14 +5715,10 @@
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2026-12-29</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -5735,27 +5741,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>水泥</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5783,22 +5789,24 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ24" s="3"/>
+      <c r="AZ24" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26特区建工MTN001</t>
+          <t>26柯资03</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 18:30</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>102683829.IB</t>
+          <t>284115.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5807,55 +5815,55 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>38.07</v>
+        <v>41.07</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>24建工02</t>
+          <t>26柯资02</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>2.46Y</t>
+          <t>2.78Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7875</t>
+          <t>1.6910</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>深圳市特区建工集团有限公司</t>
+          <t>绍兴市柯桥区国有资产投资经营集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.69</t>
+          <t>C 27.01</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5865,7 +5873,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
@@ -5879,7 +5887,7 @@
         </is>
       </c>
       <c r="U25" s="4" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
@@ -5889,38 +5897,34 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.76%~1.86%</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>广东省-深圳市</t>
+          <t>浙江省-绍兴市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据募集资金8亿元,拟用于偿还银行借款</t>
+          <t>本期债券发行规模为不超过10亿元(含10亿元),募集资金拟全部用于偿还到期公司债券的本金。[23柯资05,23柯资06]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,宁波银行股份有限公司</t>
+          <t>国信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
       <c r="AE25" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF25" s="3" t="inlineStr">
@@ -5930,17 +5934,17 @@
       </c>
       <c r="AG25" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>深圳市特区建工集团有限公司2026年度第一期中期票据</t>
+          <t>绍兴市柯桥区国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
@@ -5951,7 +5955,7 @@
       <c r="AK25" s="3"/>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -5966,32 +5970,32 @@
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6024,7 +6028,7 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP007</t>
+          <t>26东阳国资PPN002</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -6034,64 +6038,64 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>012682352.IB</t>
+          <t>032680542.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>8.1</v>
+        <v>5.0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8.1</v>
+        <v>5.0</v>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.52</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.47</v>
+        <v>1.85</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>25.72</v>
+        <v>44.42</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26广州产投SCP006</t>
+          <t>26东阳国资PPN001A</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>190D</t>
+          <t>4.50Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1.5111</t>
+          <t>1.8376</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司</t>
+          <t>东阳市国有资产投资有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C 25.95</t>
+          <t>C- 15.73</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6106,7 +6110,7 @@
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
@@ -6115,46 +6119,46 @@
         </is>
       </c>
       <c r="U26" s="4" t="n">
-        <v>1.93</v>
+        <v>4.38</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>5.33</v>
+        <v>1.7</v>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-金华市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券的发行规模为8.1亿元，募集资金全部用于偿还到期债务融资工具[26广州产投SCP001]</t>
+          <t>发行人本期拟发行规模为人民币5亿元，用于偿还有息负债[23东阳国资PPN003]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司</t>
+          <t>中信银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6169,20 +6173,24 @@
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>广州产业投资控股集团有限公司2026年度第七期超短期融资券</t>
+          <t>东阳市国有资产投资有限公司2026年度第二期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK26" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK26" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL26" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -6200,12 +6208,12 @@
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP26" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ26" s="3" t="inlineStr">
@@ -6215,17 +6223,17 @@
       </c>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr">
@@ -6258,74 +6266,66 @@
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26南电GN008(科创债)</t>
+          <t>26港兴02</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>132680099.IB</t>
+          <t>283964.SH</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>17.42</v>
+        <v>71.42</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>26南电GN007(科创债)</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>4.91Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.6296</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.6400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司</t>
+          <t>响水县港兴建设发展有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>B- 40.49</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
@@ -6349,82 +6349,84 @@
         </is>
       </c>
       <c r="U27" s="4" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>2.19</v>
+      </c>
+      <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t>1.64%~1.74%</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="X27" s="3"/>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模20亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营以及充电站项目建设</t>
+          <t>本期债券募集资金扣除发行费用和受托管理费用后,拟全部用于偿还到期债务。</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD27" s="3"/>
+          <t>开源证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr">
+        <is>
+          <t>湖南财鑫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE27" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF27" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG27" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司2026年度第八期绿色科技创新债券</t>
+          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2031-09-22</t>
-        </is>
-      </c>
-      <c r="AK27" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t/>
         </is>
       </c>
       <c r="AM27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="AN27" s="3" t="inlineStr">
@@ -6437,29 +6439,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="AP27" s="3"/>
       <c r="AQ27" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6469,7 +6467,7 @@
       </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW27" s="3" t="inlineStr">
@@ -6492,7 +6490,7 @@
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26润业投资PPN002A</t>
+          <t>26中广核租SCP006</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -6502,64 +6500,64 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>032680544.IB</t>
+          <t>012682355.IB</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>46.42</v>
+        <v>18.72</v>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>26润业01</t>
+          <t>26中广核租SCP004(绿色)</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>2.52Y+2.00Y</t>
+          <t>190D</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.8450</t>
+          <t>1.5380</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.8900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司</t>
+          <t>中广核国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 12.29</t>
+          <t>C- 15.63</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6569,12 +6567,12 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
@@ -6583,7 +6581,7 @@
         </is>
       </c>
       <c r="U28" s="4" t="n">
-        <v>2.97</v>
+        <v>2.04</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
@@ -6593,7 +6591,7 @@
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
@@ -6604,28 +6602,28 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>广东省-河源市</t>
+          <t>广东省-深圳市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
+          <t>本期债务融资工具募集资金5亿元,拟用于偿还到期银行借款</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>上海银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG28" s="3" t="inlineStr">
@@ -6635,24 +6633,20 @@
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种一)</t>
+          <t>中广核国际融资租赁有限公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK28" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-25</t>
+        </is>
+      </c>
+      <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -6670,37 +6664,37 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>8.5*无效</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6710,7 +6704,7 @@
       </c>
       <c r="AW28" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX28" s="3" t="inlineStr">
@@ -6728,7 +6722,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26中交三航SCP023</t>
+          <t>26国盛MTN004(科创债)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6738,49 +6732,49 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>012682353.IB</t>
+          <t>102683834.IB</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>0.25Y</t>
+          <t>10Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.80 ~ 2.10</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16.4</v>
+        <v>19.62</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>26中交三航SCP019</t>
+          <t>26沪盛K1</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>97D</t>
+          <t>9.94Y</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1.5002</t>
+          <t>1.9169</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
@@ -6790,12 +6784,12 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>中交第三航务工程局有限公司</t>
+          <t>上海国盛(集团)有限公司</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C 27.52</t>
+          <t>B- 46.60</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -6810,7 +6804,7 @@
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
@@ -6819,19 +6813,19 @@
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>1.54</v>
+        <v>3.212</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>1.0</v>
+        <v>1.05</v>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -6847,23 +6841,23 @@
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额为5亿元，全部用于归还发行人本部有息负债</t>
+          <t>发行人拟发行25亿元科技创新债券,其中3.5亿元用于偿还债务融资工具,21.5亿元将通过基金出资和股权投资等形式用于支持科技创新企业发展[23国盛MTN005]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司,兴业银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF29" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG29" s="3" t="inlineStr">
@@ -6873,7 +6867,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>中交第三航务工程局有限公司2026年度第二十三期超短期融资券</t>
+          <t>上海国盛(集团)有限公司2026年度第四期科技创新债券</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6883,10 +6877,14 @@
       </c>
       <c r="AJ29" s="3" t="inlineStr">
         <is>
-          <t>2026-12-29</t>
-        </is>
-      </c>
-      <c r="AK29" s="3"/>
+          <t>2036-09-28</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL29" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -6909,27 +6907,27 @@
       </c>
       <c r="AP29" s="3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ29" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR29" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>市政路桥</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
@@ -6964,108 +6962,108 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26柯资03</t>
+          <t>26夏商SCP027</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:30</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>284115.SH</t>
+          <t>012682361.IB</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.18Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.40 ~ 1.51</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>41.07</v>
+        <v>33.1</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>26夏商SCP026</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>78D</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>1.5100</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>厦门夏商集团有限公司</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>B 51.36</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>09-24 09:00</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K30" s="3" t="inlineStr">
-        <is>
-          <t>26柯资02</t>
-        </is>
-      </c>
-      <c r="L30" s="3" t="inlineStr">
-        <is>
-          <t>2.78Y</t>
-        </is>
-      </c>
-      <c r="M30" s="3" t="inlineStr">
-        <is>
-          <t>1.6910</t>
-        </is>
-      </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>绍兴市柯桥区国有资产投资经营集团有限公司</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="inlineStr">
-        <is>
-          <t>C 27.01</t>
-        </is>
-      </c>
-      <c r="Q30" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="R30" s="3" t="inlineStr">
-        <is>
-          <t>09-24 15:00</t>
-        </is>
-      </c>
-      <c r="S30" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>3.62</v>
+        <v>0.6</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7076,23 +7074,23 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>浙江省-绍兴市</t>
+          <t>福建省-厦门市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行规模为不超过10亿元(含10亿元),募集资金拟全部用于偿还到期公司债券的本金。[23柯资05,23柯资06]</t>
+          <t>发行人本期发行超短期融资券5亿元,扣除承销费后全部用于偿还发行人即将到期的债务融资工具。[26夏商SCP020]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国信证券股份有限公司</t>
+          <t>招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
       <c r="AE30" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF30" s="3" t="inlineStr">
@@ -7102,28 +7100,28 @@
       </c>
       <c r="AG30" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>绍兴市柯桥区国有资产投资经营集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>厦门夏商集团有限公司2026年度第二十七期超短期融资券</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2026-12-04</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
       <c r="AL30" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="AM30" s="3" t="inlineStr">
@@ -7138,32 +7136,32 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU30" s="3" t="inlineStr">
@@ -7196,7 +7194,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26东阳国资PPN002</t>
+          <t>26海螺集团MTN003(科创债/并购)</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7206,7 +7204,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>032680542.IB</t>
+          <t>102683836.IB</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -7215,55 +7213,55 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>44.42</v>
+        <v>17.42</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>26东阳国资PPN001A</t>
+          <t>26海螺集团MTN001(科创债)</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>4.50Y</t>
+          <t>4.46Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.8376</t>
+          <t>1.7555</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>东阳市国有资产投资有限公司</t>
+          <t>安徽海螺集团有限责任公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 15.73</t>
+          <t>C+ 33.00</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7278,7 +7276,7 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
@@ -7287,46 +7285,46 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>4.38</v>
+        <v>4.52</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.7</v>
+        <v>2.0</v>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>浙江省-金华市</t>
+          <t>安徽省-芜湖市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>发行人本期拟发行规模为人民币5亿元，用于偿还有息负债[23东阳国资PPN003]</t>
+          <t>本期科技创新债发行规模为10亿元,用于偿还发行人并购贷款和有息负债。</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,中信证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
       <c r="AE31" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF31" s="3" t="inlineStr">
@@ -7341,12 +7339,12 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>东阳市国有资产投资有限公司2026年度第二期定向债务融资工具</t>
+          <t>安徽海螺集团有限责任公司2026年度第三期科技创新债券(并购)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
@@ -7376,32 +7374,32 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>水泥</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7434,51 +7432,59 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26港兴02</t>
+          <t>26广州产投SCP007</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>09-24 19:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>283964.SH</t>
+          <t>012682352.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.0</v>
+        <v>8.1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.0</v>
+        <v>8.1</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.32 ~ 1.52</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.12</v>
+        <v>1.47</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>71.42</v>
+        <v>25.72</v>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>26广州产投SCP006</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>190D</t>
+        </is>
+      </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5111</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -7488,12 +7494,12 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>响水县港兴建设发展有限公司</t>
+          <t>广州产业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C 25.95</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7503,12 +7509,12 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
@@ -7517,44 +7523,46 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="V32" s="3"/>
+        <v>1.9259</v>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>5.33</v>
+      </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X32" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>1.50%~1.54%</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用和受托管理费用后,拟全部用于偿还到期债务。</t>
+          <t>本期超短期融资券的发行规模为8.1亿元，募集资金全部用于偿还到期债务融资工具[26广州产投SCP001]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>开源证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD32" s="3" t="inlineStr">
-        <is>
-          <t>湖南财鑫融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中国光大银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7564,78 +7572,78 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>响水县港兴建设发展有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>广州产业投资控股集团有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK32" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-25</t>
+        </is>
+      </c>
+      <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="AO32" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP32" s="3"/>
-      <c r="AQ32" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV32" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW32" s="3" t="inlineStr">
@@ -7658,7 +7666,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26乌江水电GN005</t>
+          <t>26嘉秀发展MTN004</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7668,64 +7676,64 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>132680100.IB</t>
+          <t>102683833.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.0</v>
+        <v>5.1</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.0</v>
+        <v>5.1</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.65</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>31.72</v>
+        <v>27.42</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26乌江水电GN002</t>
+          <t>26嘉秀发展MTN003</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>179D</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.5294</t>
+          <t>1.7867</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>1.5400/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江水电开发有限责任公司</t>
+          <t>嘉兴市嘉秀发展投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.45</t>
+          <t>C 27.15</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7740,7 +7748,7 @@
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
@@ -7749,51 +7757,51 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>3.0667</v>
+        <v>5.549</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>6.5</v>
+        <v>1.27</v>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.70%~1.80%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>贵州省-贵阳市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期绿色超短期融资券发行金额3亿元,募集资金将全部用于偿还构皮滩水电站等6个水电站有息负债本金</t>
+          <t>发行人本次中期票据发行金额5.10亿元,拟用于偿还发行人有息债务本金[23嘉秀发展PPN003]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,招商银行股份有限公司</t>
+          <t>杭州银行股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG33" s="3" t="inlineStr">
@@ -7803,7 +7811,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>贵州乌江水电开发有限责任公司2026年度第五期绿色超短期融资券</t>
+          <t>嘉兴市嘉秀发展投资控股集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7813,10 +7821,14 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2031-09-28</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -7834,32 +7846,32 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>水电</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7887,14 +7899,12 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ33" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ33" s="3"/>
     </row>
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26京国资SCP002</t>
+          <t>26乌江水电GN005</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7904,7 +7914,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>012682358.IB</t>
+          <t>132680100.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
@@ -7913,55 +7923,55 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.50</t>
+          <t>1.40 ~ 1.65</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>15.72</v>
+        <v>31.72</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24国管01</t>
+          <t>26乌江水电GN002</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>330D</t>
+          <t>179D</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.4873</t>
+          <t>1.5294</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.5200/1.5100</t>
+          <t>1.5400/--</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司</t>
+          <t>贵州乌江水电开发有限责任公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 35.18</t>
+          <t>C+ 30.45</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7971,12 +7981,12 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>09-24 14:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
@@ -7985,17 +7995,19 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V34" s="3"/>
+        <v>3.0667</v>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>6.5</v>
+      </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.50%~1.54%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -8003,24 +8015,20 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z34" s="3" t="inlineStr">
-        <is>
-          <t>A-1</t>
-        </is>
-      </c>
+      <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>贵州省-贵阳市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币10亿元,发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
+          <t>本期绿色超短期融资券发行金额3亿元,募集资金将全部用于偿还构皮滩水电站等6个水电站有息负债本金</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司,北京农村商业银行股份有限公司</t>
+          <t>中国银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -8031,7 +8039,7 @@
       </c>
       <c r="AF34" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG34" s="3" t="inlineStr">
@@ -8041,7 +8049,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>北京国有资本运营管理有限公司2026年度第二期超短期融资券</t>
+          <t>贵州乌江水电开发有限责任公司2026年度第五期绿色超短期融资券</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -8077,27 +8085,27 @@
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>水电</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8125,75 +8133,83 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ34" s="3"/>
+      <c r="AZ34" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26同舟02</t>
+          <t>26京国资SCP002</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>09-24 19:00</t>
+          <t>09-24 18:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>283937.SH</t>
+          <t>012682358.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F35" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.40</t>
+          <t>1.30 ~ 1.50</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>2.09</v>
+        <v>1.37</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>41.62</v>
+        <v>15.72</v>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>25中核二二GN001(科创债)</t>
+          <t>24国管01</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.24Y+2.00Y</t>
+          <t>330D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.8425</t>
+          <t>1.4873</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5200/1.5100</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P35" s="3"/>
+          <t>北京国有资本运营管理有限公司</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>B- 35.18</t>
+        </is>
+      </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -8201,31 +8217,31 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 14:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>1.85</v>
+        <v>1.2</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.30%~2.40%</t>
+          <t>1.50%~1.54%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8233,26 +8249,30 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z35" s="3"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>A-1</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
+          <t>本期债务融资工具发行规模为人民币10亿元,发行人拟将本期债务融资工具募集资金全部用于偿还债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
+          <t>华夏银行股份有限公司,北京农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -8262,71 +8282,75 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>北京国有资本运营管理有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2036-09-29</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>产业控股</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="AO35" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP35" s="3"/>
-      <c r="AQ35" s="3" t="inlineStr">
-        <is>
-          <t>建筑施工</t>
-        </is>
-      </c>
-      <c r="AR35" s="3" t="inlineStr">
-        <is>
-          <t>专业工程</t>
-        </is>
-      </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>市政路桥</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-29</t>
-        </is>
-      </c>
       <c r="AV35" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -8334,7 +8358,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8352,7 +8376,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26同舟01</t>
+          <t>26同舟02</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8362,12 +8386,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>283936.SH</t>
+          <t>283937.SH</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>3+3+4</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -8376,18 +8400,18 @@
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.80 ~ 2.40</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.86</v>
+        <v>2.09</v>
       </c>
       <c r="I36" s="4" t="n">
-        <v>18.62</v>
+        <v>41.62</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -8437,7 +8461,7 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
@@ -8447,7 +8471,7 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.95%~2.05%</t>
+          <t>2.30%~2.40%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8489,7 +8513,7 @@
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8546,7 +8570,7 @@
       </c>
       <c r="AU36" s="3" t="inlineStr">
         <is>
-          <t>2029-09-29</t>
+          <t>2031-09-29</t>
         </is>
       </c>
       <c r="AV36" s="3" t="inlineStr">
@@ -8574,76 +8598,70 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26郑州交发MTN002(绿色)</t>
+          <t>26同舟01</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>09-24 18:00</t>
+          <t>09-24 19:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>102683830.IB</t>
+          <t>283936.SH</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3+3+4</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="I37" s="4" t="n">
-        <v>41.07</v>
+        <v>18.62</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>24郑州地铁GN002</t>
+          <t>25中核二二GN001(科创债)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>1.12Y+N</t>
+          <t>2.24Y+2.00Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.6185</t>
+          <t>1.8425</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>1.6500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>C- 16.79</t>
-        </is>
-      </c>
+          <t>山东同舟产业控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P37" s="3"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>2026-09-24</t>
@@ -8651,33 +8669,31 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>--</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="V37" s="4" t="n">
-        <v>9.0</v>
-      </c>
+        <v>1.87</v>
+      </c>
+      <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.95%~2.05%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -8688,23 +8704,23 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>河南省-郑州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额上限10.00亿元,基础发行规模0亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
+          <t>本期债券募集资金7亿元拟用于偿还有息债务</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
+          <t>中泰证券股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
       <c r="AE37" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF37" s="3" t="inlineStr">
@@ -8714,73 +8730,69 @@
       </c>
       <c r="AG37" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>郑州交通发展投资集团有限公司2026年度第二期绿色中期票据</t>
+          <t>山东同舟产业控股集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2029-09-28</t>
+          <t>2036-09-29</t>
         </is>
       </c>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="AM37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP37" s="3"/>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>市政路桥</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-09-29</t>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8790,12 +8802,12 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY37" s="3" t="inlineStr">
@@ -8808,7 +8820,7 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26润业投资PPN002B</t>
+          <t>26郑州交发MTN002(绿色)</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8818,64 +8830,64 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>032680545.IB</t>
+          <t>102683830.IB</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2.5</v>
+        <v>5.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="I38" s="4" t="n">
-        <v>64.42</v>
+        <v>41.07</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26润业01</t>
+          <t>24郑州地铁GN002</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.52Y+2.00Y</t>
+          <t>1.12Y+N</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.8450</t>
+          <t>1.6185</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>1.8900/--</t>
+          <t>1.6500/--</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司</t>
+          <t>郑州交通发展投资集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C- 12.29</t>
+          <t>C- 16.79</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8885,12 +8897,12 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>09-24 15:00</t>
+          <t>09-24 09:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
@@ -8899,44 +8911,46 @@
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V38" s="3"/>
+        <v>5.62</v>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>9.0</v>
+      </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.90%~2.00%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>广东省-河源市</t>
+          <t>河南省-郑州市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
+          <t>本期发行金额上限10.00亿元,基础发行规模0亿元,拟全部安排用于归还发行人到期的债务融资工具本金[23郑州地铁GN002]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司</t>
+          <t>中国工商银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
@@ -8951,24 +8965,20 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种二)</t>
+          <t>郑州交通发展投资集团有限公司2026年度第二期绿色中期票据</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2031-09-28</t>
-        </is>
-      </c>
-      <c r="AK38" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-28</t>
+        </is>
+      </c>
+      <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
           <t>2026-09-29</t>
@@ -8991,7 +9001,7 @@
       </c>
       <c r="AP38" s="3" t="inlineStr">
         <is>
-          <t>8.5*无效</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ38" s="3" t="inlineStr">
@@ -9001,17 +9011,17 @@
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -9026,12 +9036,12 @@
       </c>
       <c r="AW38" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX38" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY38" s="3" t="inlineStr">
@@ -9044,7 +9054,7 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26国盛MTN004(科创债)</t>
+          <t>26润业投资PPN002B</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -9054,64 +9064,64 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>102683834.IB</t>
+          <t>032680545.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>10Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>25.0</v>
+        <v>2.5</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>25.0</v>
+        <v>2.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.10</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="I39" s="4" t="n">
-        <v>19.62</v>
+        <v>64.42</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26沪盛K1</t>
+          <t>26润业01</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>9.94Y</t>
+          <t>2.52Y+2.00Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.9169</t>
+          <t>1.8450</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.9500/1.9000</t>
+          <t>1.8900/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司</t>
+          <t>河源市润业投资有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>B- 46.60</t>
+          <t>C- 12.29</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -9121,12 +9131,12 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>09-24 09:00</t>
+          <t>09-24 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
@@ -9135,46 +9145,44 @@
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="V39" s="4" t="n">
-        <v>1.05</v>
-      </c>
+        <v>3.05</v>
+      </c>
+      <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.90%~2.00%</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>广东省-河源市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>发行人拟发行25亿元科技创新债券,其中3.5亿元用于偿还债务融资工具,21.5亿元将通过基金出资和股权投资等形式用于支持科技创新企业发展[23国盛MTN005]</t>
+          <t>本期定向债务融资工具基础发行规模0亿元,发行金额上限5亿元,募集资金用于偿还存量债券本金[21润业投资PPN002]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9189,17 +9197,17 @@
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>上海国盛(集团)有限公司2026年度第四期科技创新债券</t>
+          <t>河源市润业投资有限公司2026年度第二期定向债务融资工具(品种二)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2036-09-28</t>
+          <t>2031-09-28</t>
         </is>
       </c>
       <c r="AK39" s="3" t="inlineStr">
@@ -9224,32 +9232,32 @@
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP39" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>8.5*无效</t>
         </is>
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9277,9 +9285,7 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="AZ39" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ39" s="3"/>
     </row>
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-24.xlsx
+++ b/data/credit_bond_all_2026-09-24.xlsx
@@ -10934,7 +10934,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26衢产PPN001</t>
+          <t>26衢州产投PPN001</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
